--- a/public/請求書テンプレ.xlsx
+++ b/public/請求書テンプレ.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="m/d;@"/>
     <numFmt numFmtId="165" formatCode="&quot;0372785&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -58,13 +58,6 @@
       <family val="1"/>
       <color theme="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="HGP明朝E"/>
-      <charset val="128"/>
-      <family val="1"/>
-      <color theme="1"/>
-      <sz val="22"/>
     </font>
     <font>
       <name val="HGSｺﾞｼｯｸM"/>
@@ -155,15 +148,6 @@
       <sz val="16"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <i val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -187,28 +171,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -243,21 +205,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -279,34 +226,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -355,9 +274,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -373,7 +316,48 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -388,9 +372,18 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -399,34 +392,6 @@
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -435,7 +400,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -446,46 +411,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -525,18 +451,82 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium"/>
-      <top/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -548,210 +538,184 @@
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1128,48 +1092,48 @@
   <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2" outlineLevelCol="0"/>
   <cols>
-    <col width="7.109375" customWidth="1" style="56" min="1" max="4"/>
-    <col width="12.44140625" customWidth="1" style="56" min="5" max="5"/>
-    <col width="6.6640625" customWidth="1" style="56" min="6" max="7"/>
-    <col width="9.6640625" customWidth="1" style="56" min="8" max="8"/>
-    <col width="8.109375" customWidth="1" style="56" min="9" max="9"/>
-    <col width="7.44140625" customWidth="1" style="56" min="10" max="10"/>
-    <col width="7.6640625" customWidth="1" style="56" min="11" max="14"/>
-    <col width="9.6640625" customWidth="1" style="56" min="15" max="15"/>
-    <col width="10.6640625" customWidth="1" style="56" min="16" max="16"/>
-    <col width="6.6640625" customWidth="1" style="56" min="17" max="17"/>
-    <col width="7.109375" customWidth="1" style="56" min="18" max="18"/>
-    <col width="8.6640625" customWidth="1" style="56" min="19" max="19"/>
-    <col width="7.6640625" customWidth="1" style="56" min="20" max="21"/>
-    <col width="7.44140625" customWidth="1" style="56" min="22" max="22"/>
-    <col width="9.21875" bestFit="1" customWidth="1" style="56" min="24" max="24"/>
+    <col width="7.109375" customWidth="1" style="50" min="1" max="4"/>
+    <col width="12.44140625" customWidth="1" style="50" min="5" max="5"/>
+    <col width="6.6640625" customWidth="1" style="50" min="6" max="7"/>
+    <col width="9.6640625" customWidth="1" style="50" min="8" max="8"/>
+    <col width="8.109375" customWidth="1" style="50" min="9" max="9"/>
+    <col width="7.44140625" customWidth="1" style="50" min="10" max="10"/>
+    <col width="7.6640625" customWidth="1" style="50" min="11" max="14"/>
+    <col width="9.6640625" customWidth="1" style="50" min="15" max="15"/>
+    <col width="10.6640625" customWidth="1" style="50" min="16" max="16"/>
+    <col width="6.6640625" customWidth="1" style="50" min="17" max="17"/>
+    <col width="7.109375" customWidth="1" style="50" min="18" max="18"/>
+    <col width="8.6640625" customWidth="1" style="50" min="19" max="19"/>
+    <col width="7.6640625" customWidth="1" style="50" min="20" max="21"/>
+    <col width="7.44140625" customWidth="1" style="50" min="22" max="22"/>
+    <col width="9.21875" bestFit="1" customWidth="1" style="50" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.9" customHeight="1" s="56">
-      <c r="A1" s="44" t="n"/>
-      <c r="F1" s="44" t="inlineStr">
+    <row r="1" ht="24.9" customHeight="1" s="50">
+      <c r="A1" s="25" t="n"/>
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="I1" s="45" t="inlineStr">
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>請求書</t>
         </is>
       </c>
-      <c r="L1" s="44" t="n"/>
-      <c r="Q1" s="44" t="inlineStr">
+      <c r="L1" s="25" t="n"/>
+      <c r="Q1" s="25" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="T1" s="45" t="inlineStr">
+      <c r="T1" s="40" t="inlineStr">
         <is>
           <t>請求明細書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24.9" customHeight="1" s="56">
+    <row r="2" ht="24.9" customHeight="1" s="50">
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>登録番号</t>
@@ -1195,13 +1159,13 @@
       <c r="U2" s="1" t="n"/>
       <c r="V2" s="1" t="n"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="56">
+    <row r="3" ht="20.1" customHeight="1" s="50">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>工事名</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>清掃工事</t>
         </is>
@@ -1211,24 +1175,24 @@
           <t>工事名</t>
         </is>
       </c>
-      <c r="M3" s="42" t="inlineStr">
+      <c r="M3" s="43" t="inlineStr">
         <is>
           <t>清掃工事</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" s="56">
+    <row r="4" ht="20.1" customHeight="1" s="50">
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>日付：</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>月　日〆</t>
         </is>
@@ -1238,36 +1202,36 @@
           <t>日付：</t>
         </is>
       </c>
-      <c r="T4" s="43" t="inlineStr">
+      <c r="T4" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="U4" s="43" t="inlineStr">
+      <c r="U4" s="28" t="inlineStr">
         <is>
           <t>月　日〆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="56">
-      <c r="A5" s="51" t="inlineStr">
+    <row r="5" ht="20.1" customHeight="1" s="50">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="43" t="n"/>
-      <c r="L5" s="51" t="inlineStr">
+      <c r="J5" s="28" t="n"/>
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
-      <c r="U5" s="43" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" s="56">
+      <c r="U5" s="28" t="n"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" s="50">
       <c r="E6" s="0" t="inlineStr">
         <is>
           <t>　　　</t>
@@ -1279,101 +1243,101 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" s="56"/>
-    <row r="8" ht="24.9" customHeight="1" s="56"/>
-    <row r="9" ht="24.9" customHeight="1" s="56">
-      <c r="A9" s="55" t="inlineStr">
+    <row r="7" ht="20.1" customHeight="1" s="50"/>
+    <row r="8" ht="24.9" customHeight="1" s="50"/>
+    <row r="9" ht="24.9" customHeight="1" s="50">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>住所：　愛知県豊橋市東森岡1-7-13</t>
         </is>
       </c>
-      <c r="G9" s="55" t="n"/>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>金融機関名：</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>豊橋信用金庫</t>
         </is>
       </c>
-      <c r="L9" s="55" t="inlineStr">
+      <c r="L9" s="42" t="inlineStr">
         <is>
           <t>住所：　愛知県豊橋市東森岡1-7-13</t>
         </is>
       </c>
-      <c r="R9" s="55" t="n"/>
-      <c r="S9" s="40" t="n"/>
-      <c r="U9" s="39" t="n"/>
-    </row>
-    <row r="10" ht="24.9" customHeight="1" s="56">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="R9" s="42" t="n"/>
+      <c r="S9" s="20" t="n"/>
+      <c r="U9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="24.9" customHeight="1" s="50">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　TEL:　　0532-88-7770</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>支店名　：</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>牛川支店・普通</t>
         </is>
       </c>
-      <c r="L10" s="54" t="inlineStr">
+      <c r="L10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　TEL:　　0532-88-7770</t>
         </is>
       </c>
-      <c r="S10" s="40" t="n"/>
-      <c r="U10" s="39" t="n"/>
-    </row>
-    <row r="11" ht="24.9" customHeight="1" s="56">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="S10" s="20" t="n"/>
+      <c r="U10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="24.9" customHeight="1" s="50">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　FAX:　　0532-88-4591</t>
         </is>
       </c>
-      <c r="H11" s="40" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>口座名義：</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　FAX:　　0532-88-4591</t>
         </is>
       </c>
-      <c r="S11" s="40" t="n"/>
-      <c r="U11" s="39" t="n"/>
-    </row>
-    <row r="12" ht="24.9" customHeight="1" s="56">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="S11" s="20" t="n"/>
+      <c r="U11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="24.9" customHeight="1" s="50">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>E-MAIL:　cs-yuzuki0109@cd5.so-net.ne.ip</t>
         </is>
       </c>
-      <c r="H12" s="39" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　代表取締役　藤澤　淳</t>
         </is>
       </c>
-      <c r="L12" s="55" t="inlineStr">
+      <c r="L12" s="42" t="inlineStr">
         <is>
           <t>E-MAIL:　cs-yuzuki0109@cd5.so-net.ne.ip</t>
         </is>
       </c>
-      <c r="S12" s="39" t="n"/>
-    </row>
-    <row r="13" ht="24.9" customHeight="1" s="56">
+      <c r="S12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="24.9" customHeight="1" s="50">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
@@ -1381,12 +1345,12 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="40" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>口座番号：</t>
         </is>
       </c>
-      <c r="J13" s="57" t="n">
+      <c r="J13" s="51" t="n">
         <v>372785</v>
       </c>
       <c r="L13" s="5" t="n"/>
@@ -1396,10 +1360,10 @@
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="40" t="n"/>
-      <c r="U13" s="57" t="n"/>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" s="56">
+      <c r="S13" s="20" t="n"/>
+      <c r="U13" s="51" t="n"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" s="50">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
@@ -1415,729 +1379,718 @@
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" s="56" thickBot="1">
+    <row r="15" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="C15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="56">
-      <c r="A16" s="58" t="inlineStr">
+    <row r="16" ht="21.75" customHeight="1" s="50">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="44" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="H16" s="37" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="J16" s="59" t="n"/>
-      <c r="K16" s="60" t="n"/>
-      <c r="L16" s="58" t="inlineStr">
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
         </is>
       </c>
-      <c r="M16" s="59" t="n"/>
-      <c r="N16" s="59" t="n"/>
-      <c r="O16" s="60" t="n"/>
-      <c r="P16" s="37" t="inlineStr">
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="44" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="Q16" s="37" t="inlineStr">
+      <c r="Q16" s="44" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="37" t="inlineStr">
+      <c r="R16" s="57" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="37" t="inlineStr">
+      <c r="S16" s="57" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="37" t="inlineStr">
+      <c r="T16" s="57" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="U16" s="59" t="n"/>
-      <c r="V16" s="61" t="n"/>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" s="56">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="U16" s="34" t="n"/>
+      <c r="V16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" s="50">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>清掃工事</t>
         </is>
       </c>
-      <c r="B17" s="62" t="n"/>
-      <c r="C17" s="62" t="n"/>
-      <c r="D17" s="63" t="n"/>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="28">
+      <c r="I17" s="62">
         <f>T35</f>
         <v/>
       </c>
-      <c r="J17" s="62" t="n"/>
-      <c r="K17" s="63" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="62" t="n"/>
-      <c r="N17" s="62" t="n"/>
-      <c r="O17" s="63" t="n"/>
-      <c r="P17" s="64" t="n"/>
-      <c r="Q17" s="27" t="n"/>
-      <c r="R17" s="27" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="28">
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="26" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="53" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="63" t="n"/>
+      <c r="S17" s="64" t="n"/>
+      <c r="T17" s="58">
         <f>S17*Q17</f>
         <v/>
       </c>
-      <c r="U17" s="62" t="n"/>
-      <c r="V17" s="65" t="n"/>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" s="56">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="62" t="n"/>
-      <c r="C18" s="62" t="n"/>
-      <c r="D18" s="63" t="n"/>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
+      <c r="U17" s="18" t="n"/>
+      <c r="V17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" s="50">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n"/>
-      <c r="I18" s="28">
+      <c r="I18" s="62">
         <f>H18*F18</f>
         <v/>
       </c>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="63" t="n"/>
-      <c r="L18" s="29" t="n"/>
-      <c r="M18" s="62" t="n"/>
-      <c r="N18" s="62" t="n"/>
-      <c r="O18" s="63" t="n"/>
-      <c r="P18" s="64" t="n"/>
-      <c r="Q18" s="27" t="n"/>
-      <c r="R18" s="27" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="28">
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="26" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="53" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="63" t="n"/>
+      <c r="S18" s="64" t="n"/>
+      <c r="T18" s="58">
         <f>S18*Q18</f>
         <v/>
       </c>
-      <c r="U18" s="62" t="n"/>
-      <c r="V18" s="65" t="n"/>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" s="56">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="62" t="n"/>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="63" t="n"/>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
+      <c r="U18" s="18" t="n"/>
+      <c r="V18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="50">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="28">
+      <c r="I19" s="62">
         <f>H19*F19</f>
         <v/>
       </c>
-      <c r="J19" s="62" t="n"/>
-      <c r="K19" s="63" t="n"/>
-      <c r="L19" s="29" t="n"/>
-      <c r="M19" s="62" t="n"/>
-      <c r="N19" s="62" t="n"/>
-      <c r="O19" s="63" t="n"/>
-      <c r="P19" s="64" t="n"/>
-      <c r="Q19" s="27" t="n"/>
-      <c r="R19" s="27" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="28">
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="26" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="18" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="53" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="63" t="n"/>
+      <c r="S19" s="64" t="n"/>
+      <c r="T19" s="58">
         <f>S19*Q19</f>
         <v/>
       </c>
-      <c r="U19" s="62" t="n"/>
-      <c r="V19" s="65" t="n"/>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" s="56">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="63" t="n"/>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
+      <c r="U19" s="18" t="n"/>
+      <c r="V19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" s="50">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n"/>
-      <c r="I20" s="28">
+      <c r="I20" s="62">
         <f>H20*F20</f>
         <v/>
       </c>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="63" t="n"/>
-      <c r="L20" s="29" t="n"/>
-      <c r="M20" s="62" t="n"/>
-      <c r="N20" s="62" t="n"/>
-      <c r="O20" s="63" t="n"/>
-      <c r="P20" s="64" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="9" t="n"/>
-      <c r="T20" s="28">
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="26" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="53" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="63" t="n"/>
+      <c r="S20" s="64" t="n"/>
+      <c r="T20" s="58">
         <f>S20*Q20</f>
         <v/>
       </c>
-      <c r="U20" s="62" t="n"/>
-      <c r="V20" s="65" t="n"/>
-    </row>
-    <row r="21" ht="20.1" customHeight="1" s="56">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="62" t="n"/>
-      <c r="C21" s="62" t="n"/>
-      <c r="D21" s="63" t="n"/>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
+      <c r="U20" s="18" t="n"/>
+      <c r="V20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" s="50">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="28">
+      <c r="I21" s="62">
         <f>H21*F21</f>
         <v/>
       </c>
-      <c r="J21" s="62" t="n"/>
-      <c r="K21" s="63" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="62" t="n"/>
-      <c r="N21" s="62" t="n"/>
-      <c r="O21" s="63" t="n"/>
-      <c r="P21" s="64" t="n"/>
-      <c r="Q21" s="27" t="n"/>
-      <c r="R21" s="27" t="n"/>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="28">
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="26" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="53" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="63" t="n"/>
+      <c r="S21" s="64" t="n"/>
+      <c r="T21" s="58">
         <f>S21*Q21</f>
         <v/>
       </c>
-      <c r="U21" s="62" t="n"/>
-      <c r="V21" s="65" t="n"/>
-    </row>
-    <row r="22" ht="20.1" customHeight="1" s="56">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="62" t="n"/>
-      <c r="C22" s="62" t="n"/>
-      <c r="D22" s="63" t="n"/>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="50">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
-      <c r="I22" s="28">
+      <c r="I22" s="62">
         <f>H22*F22</f>
         <v/>
       </c>
-      <c r="J22" s="62" t="n"/>
-      <c r="K22" s="63" t="n"/>
-      <c r="L22" s="29" t="n"/>
-      <c r="M22" s="62" t="n"/>
-      <c r="N22" s="62" t="n"/>
-      <c r="O22" s="63" t="n"/>
-      <c r="P22" s="64" t="n"/>
-      <c r="Q22" s="27" t="n"/>
-      <c r="R22" s="27" t="n"/>
-      <c r="S22" s="9" t="n"/>
-      <c r="T22" s="28">
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="26" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="53" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="63" t="n"/>
+      <c r="S22" s="64" t="n"/>
+      <c r="T22" s="58">
         <f>S22*Q22</f>
         <v/>
       </c>
-      <c r="U22" s="62" t="n"/>
-      <c r="V22" s="65" t="n"/>
-    </row>
-    <row r="23" ht="20.1" customHeight="1" s="56">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="62" t="n"/>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="63" t="n"/>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+      <c r="U22" s="18" t="n"/>
+      <c r="V22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" s="50">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="28">
+      <c r="I23" s="62">
         <f>H23*F23</f>
         <v/>
       </c>
-      <c r="J23" s="62" t="n"/>
-      <c r="K23" s="63" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="62" t="n"/>
-      <c r="N23" s="62" t="n"/>
-      <c r="O23" s="63" t="n"/>
-      <c r="P23" s="64" t="n"/>
-      <c r="Q23" s="27" t="n"/>
-      <c r="R23" s="27" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="28">
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="26" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="53" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="63" t="n"/>
+      <c r="S23" s="64" t="n"/>
+      <c r="T23" s="58">
         <f>S23*Q23</f>
         <v/>
       </c>
-      <c r="U23" s="62" t="n"/>
-      <c r="V23" s="65" t="n"/>
-    </row>
-    <row r="24" ht="20.1" customHeight="1" s="56">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="62" t="n"/>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="63" t="n"/>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+      <c r="U23" s="18" t="n"/>
+      <c r="V23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" s="50">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="28">
+      <c r="I24" s="62">
         <f>H24*F24</f>
         <v/>
       </c>
-      <c r="J24" s="62" t="n"/>
-      <c r="K24" s="63" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="62" t="n"/>
-      <c r="N24" s="62" t="n"/>
-      <c r="O24" s="63" t="n"/>
-      <c r="P24" s="64" t="n"/>
-      <c r="Q24" s="27" t="n"/>
-      <c r="R24" s="27" t="n"/>
-      <c r="S24" s="9" t="n"/>
-      <c r="T24" s="28">
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="26" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="19" t="n"/>
+      <c r="P24" s="53" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="63" t="n"/>
+      <c r="S24" s="64" t="n"/>
+      <c r="T24" s="58">
         <f>S24*Q24</f>
         <v/>
       </c>
-      <c r="U24" s="62" t="n"/>
-      <c r="V24" s="65" t="n"/>
-    </row>
-    <row r="25" ht="20.1" customHeight="1" s="56">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="62" t="n"/>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="63" t="n"/>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+      <c r="U24" s="18" t="n"/>
+      <c r="V24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" s="50">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="28">
+      <c r="I25" s="62">
         <f>H25*F25</f>
         <v/>
       </c>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="63" t="n"/>
-      <c r="L25" s="29" t="n"/>
-      <c r="M25" s="62" t="n"/>
-      <c r="N25" s="62" t="n"/>
-      <c r="O25" s="63" t="n"/>
-      <c r="P25" s="64" t="n"/>
-      <c r="Q25" s="27" t="n"/>
-      <c r="R25" s="27" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="28">
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="53" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="63" t="n"/>
+      <c r="S25" s="64" t="n"/>
+      <c r="T25" s="58">
         <f>S25*Q25</f>
         <v/>
       </c>
-      <c r="U25" s="62" t="n"/>
-      <c r="V25" s="65" t="n"/>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" s="56">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="62" t="n"/>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="63" t="n"/>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
+      <c r="U25" s="18" t="n"/>
+      <c r="V25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="50">
+      <c r="A26" s="22" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="28">
+      <c r="I26" s="62">
         <f>H26*F26</f>
         <v/>
       </c>
-      <c r="J26" s="62" t="n"/>
-      <c r="K26" s="63" t="n"/>
-      <c r="L26" s="29" t="n"/>
-      <c r="M26" s="62" t="n"/>
-      <c r="N26" s="62" t="n"/>
-      <c r="O26" s="63" t="n"/>
-      <c r="P26" s="64" t="n"/>
-      <c r="Q26" s="27" t="n"/>
-      <c r="R26" s="27" t="n"/>
-      <c r="S26" s="9" t="n"/>
-      <c r="T26" s="28">
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="26" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="53" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="63" t="n"/>
+      <c r="S26" s="64" t="n"/>
+      <c r="T26" s="58">
         <f>S26*Q26</f>
         <v/>
       </c>
-      <c r="U26" s="62" t="n"/>
-      <c r="V26" s="65" t="n"/>
-    </row>
-    <row r="27" ht="20.1" customHeight="1" s="56">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="62" t="n"/>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="63" t="n"/>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
+      <c r="U26" s="18" t="n"/>
+      <c r="V26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="50">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="28">
+      <c r="I27" s="62">
         <f>H27*F27</f>
         <v/>
       </c>
-      <c r="J27" s="62" t="n"/>
-      <c r="K27" s="63" t="n"/>
-      <c r="L27" s="29" t="n"/>
-      <c r="M27" s="62" t="n"/>
-      <c r="N27" s="62" t="n"/>
-      <c r="O27" s="63" t="n"/>
-      <c r="P27" s="64" t="n"/>
-      <c r="Q27" s="27" t="n"/>
-      <c r="R27" s="27" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="28">
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="26" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="53" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="63" t="n"/>
+      <c r="S27" s="64" t="n"/>
+      <c r="T27" s="58">
         <f>S27*Q27</f>
         <v/>
       </c>
-      <c r="U27" s="62" t="n"/>
-      <c r="V27" s="65" t="n"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1" s="56">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="62" t="n"/>
-      <c r="C28" s="62" t="n"/>
-      <c r="D28" s="63" t="n"/>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="U27" s="18" t="n"/>
+      <c r="V27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" s="50">
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="28">
+      <c r="I28" s="62">
         <f>H28*F28</f>
         <v/>
       </c>
-      <c r="J28" s="62" t="n"/>
-      <c r="K28" s="63" t="n"/>
-      <c r="L28" s="29" t="n"/>
-      <c r="M28" s="62" t="n"/>
-      <c r="N28" s="62" t="n"/>
-      <c r="O28" s="63" t="n"/>
-      <c r="P28" s="64" t="n"/>
-      <c r="Q28" s="27" t="n"/>
-      <c r="R28" s="27" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="28">
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="26" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="19" t="n"/>
+      <c r="P28" s="53" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="63" t="n"/>
+      <c r="S28" s="64" t="n"/>
+      <c r="T28" s="58">
         <f>S28*Q28</f>
         <v/>
       </c>
-      <c r="U28" s="62" t="n"/>
-      <c r="V28" s="65" t="n"/>
-    </row>
-    <row r="29" ht="20.1" customHeight="1" s="56">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="62" t="n"/>
-      <c r="C29" s="62" t="n"/>
-      <c r="D29" s="63" t="n"/>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" s="50">
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="28">
+      <c r="I29" s="62">
         <f>H29*F29</f>
         <v/>
       </c>
-      <c r="J29" s="62" t="n"/>
-      <c r="K29" s="63" t="n"/>
-      <c r="L29" s="29" t="n"/>
-      <c r="M29" s="62" t="n"/>
-      <c r="N29" s="62" t="n"/>
-      <c r="O29" s="63" t="n"/>
-      <c r="P29" s="64" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
-      <c r="S29" s="10" t="n"/>
-      <c r="T29" s="28">
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="26" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="53" t="n"/>
+      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="63" t="n"/>
+      <c r="S29" s="65" t="n"/>
+      <c r="T29" s="58">
         <f>S29*Q29</f>
         <v/>
       </c>
-      <c r="U29" s="62" t="n"/>
-      <c r="V29" s="65" t="n"/>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" s="56">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="62" t="n"/>
-      <c r="C30" s="62" t="n"/>
-      <c r="D30" s="63" t="n"/>
-      <c r="E30" s="66" t="n"/>
+      <c r="U29" s="18" t="n"/>
+      <c r="V29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" s="50">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="55" t="n"/>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="28">
+      <c r="I30" s="62">
         <f>H30*F30</f>
         <v/>
       </c>
-      <c r="J30" s="62" t="n"/>
-      <c r="K30" s="63" t="n"/>
-      <c r="L30" s="29" t="n"/>
-      <c r="M30" s="62" t="n"/>
-      <c r="N30" s="62" t="n"/>
-      <c r="O30" s="63" t="n"/>
-      <c r="P30" s="66" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="26" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="19" t="n"/>
+      <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="10" t="n"/>
-      <c r="T30" s="28">
+      <c r="R30" s="66" t="n"/>
+      <c r="S30" s="65" t="n"/>
+      <c r="T30" s="58">
         <f>S30*Q30</f>
         <v/>
       </c>
-      <c r="U30" s="62" t="n"/>
-      <c r="V30" s="65" t="n"/>
-    </row>
-    <row r="31" ht="20.1" customHeight="1" s="56">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="62" t="n"/>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="63" t="n"/>
-      <c r="E31" s="66" t="n"/>
+      <c r="U30" s="18" t="n"/>
+      <c r="V30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" s="50">
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="55" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="28">
+      <c r="I31" s="62">
         <f>H31*F31</f>
         <v/>
       </c>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="63" t="n"/>
-      <c r="L31" s="29" t="n"/>
-      <c r="M31" s="62" t="n"/>
-      <c r="N31" s="62" t="n"/>
-      <c r="O31" s="63" t="n"/>
-      <c r="P31" s="66" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="26" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="10" t="n"/>
-      <c r="T31" s="28">
+      <c r="R31" s="66" t="n"/>
+      <c r="S31" s="65" t="n"/>
+      <c r="T31" s="58">
         <f>S31*Q31</f>
         <v/>
       </c>
-      <c r="U31" s="62" t="n"/>
-      <c r="V31" s="65" t="n"/>
-    </row>
-    <row r="32" ht="20.1" customHeight="1" s="56">
-      <c r="A32" s="26" t="n"/>
-      <c r="B32" s="62" t="n"/>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="63" t="n"/>
-      <c r="E32" s="66" t="n"/>
+      <c r="U31" s="18" t="n"/>
+      <c r="V31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" s="50">
+      <c r="A32" s="47" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="55" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="28">
+      <c r="I32" s="62">
         <f>H32*F32</f>
         <v/>
       </c>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="63" t="n"/>
-      <c r="L32" s="47" t="n"/>
-      <c r="M32" s="62" t="n"/>
-      <c r="N32" s="62" t="n"/>
-      <c r="O32" s="63" t="n"/>
-      <c r="P32" s="66" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="26" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="19" t="n"/>
+      <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="28">
+      <c r="R32" s="66" t="n"/>
+      <c r="S32" s="66" t="n"/>
+      <c r="T32" s="58">
         <f>S32*Q32</f>
         <v/>
       </c>
-      <c r="U32" s="62" t="n"/>
-      <c r="V32" s="65" t="n"/>
-    </row>
-    <row r="33" ht="20.1" customHeight="1" s="56">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="U32" s="18" t="n"/>
+      <c r="V32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" s="50">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="B33" s="62" t="n"/>
-      <c r="C33" s="62" t="n"/>
-      <c r="D33" s="62" t="n"/>
-      <c r="E33" s="62" t="n"/>
-      <c r="F33" s="62" t="n"/>
-      <c r="G33" s="62" t="n"/>
-      <c r="H33" s="63" t="n"/>
-      <c r="I33" s="28">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="62">
         <f>I17</f>
         <v/>
       </c>
-      <c r="J33" s="62" t="n"/>
-      <c r="K33" s="63" t="n"/>
-      <c r="L33" s="29" t="n"/>
-      <c r="M33" s="62" t="n"/>
-      <c r="N33" s="62" t="n"/>
-      <c r="O33" s="63" t="n"/>
-      <c r="P33" s="66" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="26" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="19" t="n"/>
+      <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="11" t="n"/>
-      <c r="S33" s="10" t="n"/>
-      <c r="T33" s="28">
+      <c r="R33" s="66" t="n"/>
+      <c r="S33" s="65" t="n"/>
+      <c r="T33" s="58">
         <f>S33*Q33</f>
         <v/>
       </c>
-      <c r="U33" s="62" t="n"/>
-      <c r="V33" s="65" t="n"/>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" s="56">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="U33" s="18" t="n"/>
+      <c r="V33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" s="50">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>消費税10％</t>
         </is>
       </c>
-      <c r="B34" s="62" t="n"/>
-      <c r="C34" s="62" t="n"/>
-      <c r="D34" s="62" t="n"/>
-      <c r="E34" s="62" t="n"/>
-      <c r="F34" s="62" t="n"/>
-      <c r="G34" s="62" t="n"/>
-      <c r="H34" s="63" t="n"/>
-      <c r="I34" s="19">
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="67">
         <f>I33*10%</f>
         <v/>
       </c>
-      <c r="J34" s="62" t="n"/>
-      <c r="K34" s="63" t="n"/>
-      <c r="L34" s="47" t="n"/>
-      <c r="M34" s="62" t="n"/>
-      <c r="N34" s="62" t="n"/>
-      <c r="O34" s="63" t="n"/>
-      <c r="P34" s="66" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="26" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="19" t="n"/>
+      <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="11" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="28">
+      <c r="R34" s="66" t="n"/>
+      <c r="S34" s="66" t="n"/>
+      <c r="T34" s="58">
         <f>S34*Q34</f>
         <v/>
       </c>
-      <c r="U34" s="62" t="n"/>
-      <c r="V34" s="65" t="n"/>
-    </row>
-    <row r="35" ht="20.1" customHeight="1" s="56" thickBot="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="U34" s="18" t="n"/>
+      <c r="V34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="67" t="n"/>
-      <c r="C35" s="67" t="n"/>
-      <c r="D35" s="67" t="n"/>
-      <c r="E35" s="67" t="n"/>
-      <c r="F35" s="67" t="n"/>
-      <c r="G35" s="67" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="69">
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="29">
         <f>I33+I34</f>
         <v/>
       </c>
-      <c r="J35" s="67" t="n"/>
-      <c r="K35" s="74" t="n"/>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="36" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="M35" s="62" t="n"/>
-      <c r="N35" s="62" t="n"/>
-      <c r="O35" s="62" t="n"/>
-      <c r="P35" s="62" t="n"/>
-      <c r="Q35" s="62" t="n"/>
-      <c r="R35" s="62" t="n"/>
-      <c r="S35" s="63" t="n"/>
-      <c r="T35" s="28">
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="18" t="n"/>
+      <c r="S35" s="19" t="n"/>
+      <c r="T35" s="58">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
-      <c r="U35" s="62" t="n"/>
-      <c r="V35" s="65" t="n"/>
-    </row>
-    <row r="36" ht="20.1" customHeight="1" s="56">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="U35" s="18" t="n"/>
+      <c r="V35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" s="50">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>今後ともよろしくお願い申し上げます。</t>
         </is>
       </c>
-      <c r="B36" s="71" t="n"/>
-      <c r="C36" s="71" t="n"/>
-      <c r="D36" s="71" t="n"/>
-      <c r="E36" s="71" t="n"/>
-      <c r="F36" s="71" t="n"/>
-      <c r="G36" s="71" t="n"/>
-      <c r="H36" s="71" t="n"/>
-      <c r="I36" s="71" t="n"/>
-      <c r="J36" s="71" t="n"/>
-      <c r="K36" s="72" t="n"/>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="L36" s="36" t="inlineStr">
         <is>
           <t>消費税10％</t>
         </is>
       </c>
-      <c r="M36" s="62" t="n"/>
-      <c r="N36" s="62" t="n"/>
-      <c r="O36" s="62" t="n"/>
-      <c r="P36" s="62" t="n"/>
-      <c r="Q36" s="62" t="n"/>
-      <c r="R36" s="62" t="n"/>
-      <c r="S36" s="63" t="n"/>
-      <c r="T36" s="19">
+      <c r="M36" s="18" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="R36" s="18" t="n"/>
+      <c r="S36" s="19" t="n"/>
+      <c r="T36" s="59">
         <f>T35*10%</f>
         <v/>
       </c>
-      <c r="U36" s="62" t="n"/>
-      <c r="V36" s="65" t="n"/>
-    </row>
-    <row r="37" ht="20.1" customHeight="1" s="56" thickBot="1">
-      <c r="K37" s="73" t="n"/>
-      <c r="L37" s="21" t="inlineStr">
+      <c r="U36" s="18" t="n"/>
+      <c r="V36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
+      <c r="L37" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="M37" s="67" t="n"/>
-      <c r="N37" s="67" t="n"/>
-      <c r="O37" s="67" t="n"/>
-      <c r="P37" s="67" t="n"/>
-      <c r="Q37" s="67" t="n"/>
-      <c r="R37" s="67" t="n"/>
-      <c r="S37" s="68" t="n"/>
-      <c r="T37" s="69">
+      <c r="M37" s="30" t="n"/>
+      <c r="N37" s="30" t="n"/>
+      <c r="O37" s="30" t="n"/>
+      <c r="P37" s="30" t="n"/>
+      <c r="Q37" s="30" t="n"/>
+      <c r="R37" s="30" t="n"/>
+      <c r="S37" s="39" t="n"/>
+      <c r="T37" s="60">
         <f>T35+T36</f>
         <v/>
       </c>
-      <c r="U37" s="67" t="n"/>
-      <c r="V37" s="70" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" s="56">
+      <c r="U37" s="30" t="n"/>
+      <c r="V37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="12" customHeight="1" s="50">
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -2171,8 +2124,8 @@
     <mergeCell ref="L1:P2"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="L27:O27"/>
-    <mergeCell ref="J9:K9"/>
     <mergeCell ref="I24:K24"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="L17:O17"/>
@@ -2255,8 +2208,8 @@
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="L24:O24"/>
     <mergeCell ref="L18:O18"/>
+    <mergeCell ref="L33:O33"/>
     <mergeCell ref="T33:V33"/>
-    <mergeCell ref="L33:O33"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="L26:O26"/>
     <mergeCell ref="A21:D21"/>
@@ -2317,30 +2270,30 @@
   <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2" outlineLevelCol="0"/>
   <cols>
-    <col width="7.109375" customWidth="1" style="56" min="1" max="4"/>
-    <col width="12.44140625" customWidth="1" style="56" min="5" max="5"/>
-    <col width="6.6640625" customWidth="1" style="56" min="6" max="7"/>
-    <col width="9.6640625" customWidth="1" style="56" min="8" max="8"/>
-    <col width="8.109375" customWidth="1" style="56" min="9" max="9"/>
-    <col width="7.44140625" customWidth="1" style="56" min="10" max="10"/>
-    <col width="7.6640625" customWidth="1" style="56" min="11" max="11"/>
-    <col width="9.21875" bestFit="1" customWidth="1" style="56" min="13" max="13"/>
+    <col width="7.109375" customWidth="1" style="50" min="1" max="4"/>
+    <col width="12.44140625" customWidth="1" style="50" min="5" max="5"/>
+    <col width="6.6640625" customWidth="1" style="50" min="6" max="7"/>
+    <col width="9.6640625" customWidth="1" style="50" min="8" max="8"/>
+    <col width="8.109375" customWidth="1" style="50" min="9" max="9"/>
+    <col width="7.44140625" customWidth="1" style="50" min="10" max="10"/>
+    <col width="7.6640625" customWidth="1" style="50" min="11" max="11"/>
+    <col width="9.21875" bestFit="1" customWidth="1" style="50" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.9" customHeight="1" s="56">
-      <c r="A1" s="44" t="n"/>
-      <c r="F1" s="44" t="inlineStr">
+    <row r="1" ht="24.9" customHeight="1" s="50">
+      <c r="A1" s="25" t="n"/>
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="I1" s="45" t="inlineStr">
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>請求書兼明細書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24.9" customHeight="1" s="56">
+    <row r="2" ht="24.9" customHeight="1" s="50">
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>登録番号</t>
@@ -2354,119 +2307,119 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="56">
+    <row r="3" ht="20.1" customHeight="1" s="50">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>工事名</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>清掃工事</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" s="56">
+    <row r="4" ht="20.1" customHeight="1" s="50">
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>日付：</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>月　日〆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="56">
-      <c r="A5" s="51" t="inlineStr">
+    <row r="5" ht="20.1" customHeight="1" s="50">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="43" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" s="56">
+      <c r="J5" s="28" t="n"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" s="50">
       <c r="E6" s="0" t="inlineStr">
         <is>
           <t>　　　</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" s="56"/>
-    <row r="8" ht="24.9" customHeight="1" s="56"/>
-    <row r="9" ht="24.9" customHeight="1" s="56">
-      <c r="A9" s="55" t="inlineStr">
+    <row r="7" ht="20.1" customHeight="1" s="50"/>
+    <row r="8" ht="24.9" customHeight="1" s="50"/>
+    <row r="9" ht="24.9" customHeight="1" s="50">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>住所：　愛知県豊橋市東森岡1-7-13</t>
         </is>
       </c>
-      <c r="G9" s="55" t="n"/>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>金融機関名：</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>豊橋信用金庫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24.9" customHeight="1" s="56">
-      <c r="A10" s="54" t="inlineStr">
+    <row r="10" ht="24.9" customHeight="1" s="50">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　TEL:　　0532-88-7770</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>支店名　：</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>牛川支店・普通</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24.9" customHeight="1" s="56">
-      <c r="A11" s="53" t="inlineStr">
+    <row r="11" ht="24.9" customHeight="1" s="50">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　FAX:　　0532-88-4591</t>
         </is>
       </c>
-      <c r="H11" s="40" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>口座名義：</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24.9" customHeight="1" s="56">
-      <c r="A12" s="55" t="inlineStr">
+    <row r="12" ht="24.9" customHeight="1" s="50">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>E-MAIL:　cs-yuzuki0109@cd5.so-net.ne.ip</t>
         </is>
       </c>
-      <c r="H12" s="39" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　代表取締役　藤澤　淳</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24.9" customHeight="1" s="56">
+    <row r="13" ht="24.9" customHeight="1" s="50">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
@@ -2474,16 +2427,16 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="40" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>口座番号：</t>
         </is>
       </c>
-      <c r="J13" s="57" t="n">
+      <c r="J13" s="51" t="n">
         <v>372785</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" s="56">
+    <row r="14" ht="20.1" customHeight="1" s="50">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
@@ -2492,383 +2445,371 @@
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" s="56" thickBot="1">
+    <row r="15" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="C15" s="6" t="n"/>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="56">
-      <c r="A16" s="58" t="inlineStr">
+    <row r="16" ht="21.75" customHeight="1" s="50">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="44" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="H16" s="37" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="J16" s="59" t="n"/>
-      <c r="K16" s="60" t="n"/>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" s="56">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="62" t="n"/>
-      <c r="C17" s="62" t="n"/>
-      <c r="D17" s="63" t="n"/>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" s="50">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="28">
+      <c r="I17" s="62">
         <f>H17*F17</f>
         <v/>
       </c>
-      <c r="J17" s="62" t="n"/>
-      <c r="K17" s="63" t="n"/>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" s="56">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="62" t="n"/>
-      <c r="C18" s="62" t="n"/>
-      <c r="D18" s="63" t="n"/>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" s="50">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n"/>
-      <c r="I18" s="28">
+      <c r="I18" s="62">
         <f>H18*F18</f>
         <v/>
       </c>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="63" t="n"/>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" s="56">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="62" t="n"/>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="63" t="n"/>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="50">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="28">
+      <c r="I19" s="62">
         <f>H19*F19</f>
         <v/>
       </c>
-      <c r="J19" s="62" t="n"/>
-      <c r="K19" s="63" t="n"/>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" s="56">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="63" t="n"/>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" s="50">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n"/>
-      <c r="I20" s="28">
+      <c r="I20" s="62">
         <f>H20*F20</f>
         <v/>
       </c>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="63" t="n"/>
-    </row>
-    <row r="21" ht="20.1" customHeight="1" s="56">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="62" t="n"/>
-      <c r="C21" s="62" t="n"/>
-      <c r="D21" s="63" t="n"/>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="26" t="n"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" s="50">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="28">
+      <c r="I21" s="62">
         <f>H21*F21</f>
         <v/>
       </c>
-      <c r="J21" s="62" t="n"/>
-      <c r="K21" s="63" t="n"/>
-    </row>
-    <row r="22" ht="20.1" customHeight="1" s="56">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="62" t="n"/>
-      <c r="C22" s="62" t="n"/>
-      <c r="D22" s="63" t="n"/>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="26" t="n"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="50">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
-      <c r="I22" s="28">
+      <c r="I22" s="62">
         <f>H22*F22</f>
         <v/>
       </c>
-      <c r="J22" s="62" t="n"/>
-      <c r="K22" s="63" t="n"/>
-    </row>
-    <row r="23" ht="20.1" customHeight="1" s="56">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="62" t="n"/>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="63" t="n"/>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="26" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" s="50">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="28">
+      <c r="I23" s="62">
         <f>H23*F23</f>
         <v/>
       </c>
-      <c r="J23" s="62" t="n"/>
-      <c r="K23" s="63" t="n"/>
-    </row>
-    <row r="24" ht="20.1" customHeight="1" s="56">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="62" t="n"/>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="63" t="n"/>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="26" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" s="50">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="28">
+      <c r="I24" s="62">
         <f>H24*F24</f>
         <v/>
       </c>
-      <c r="J24" s="62" t="n"/>
-      <c r="K24" s="63" t="n"/>
-    </row>
-    <row r="25" ht="20.1" customHeight="1" s="56">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="62" t="n"/>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="63" t="n"/>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" s="50">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="28">
+      <c r="I25" s="62">
         <f>H25*F25</f>
         <v/>
       </c>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="63" t="n"/>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" s="56">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="62" t="n"/>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="63" t="n"/>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="50">
+      <c r="A26" s="22" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="28">
+      <c r="I26" s="62">
         <f>H26*F26</f>
         <v/>
       </c>
-      <c r="J26" s="62" t="n"/>
-      <c r="K26" s="63" t="n"/>
-    </row>
-    <row r="27" ht="20.1" customHeight="1" s="56">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="62" t="n"/>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="63" t="n"/>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="26" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="50">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="28">
+      <c r="I27" s="62">
         <f>H27*F27</f>
         <v/>
       </c>
-      <c r="J27" s="62" t="n"/>
-      <c r="K27" s="63" t="n"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1" s="56">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="62" t="n"/>
-      <c r="C28" s="62" t="n"/>
-      <c r="D28" s="63" t="n"/>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="26" t="n"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" s="50">
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="28">
+      <c r="I28" s="62">
         <f>H28*F28</f>
         <v/>
       </c>
-      <c r="J28" s="62" t="n"/>
-      <c r="K28" s="63" t="n"/>
-    </row>
-    <row r="29" ht="20.1" customHeight="1" s="56">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="62" t="n"/>
-      <c r="C29" s="62" t="n"/>
-      <c r="D29" s="63" t="n"/>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="26" t="n"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" s="50">
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="28">
+      <c r="I29" s="62">
         <f>H29*F29</f>
         <v/>
       </c>
-      <c r="J29" s="62" t="n"/>
-      <c r="K29" s="63" t="n"/>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" s="56">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="62" t="n"/>
-      <c r="C30" s="62" t="n"/>
-      <c r="D30" s="63" t="n"/>
-      <c r="E30" s="66" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="26" t="n"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" s="50">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="55" t="n"/>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="28">
+      <c r="I30" s="62">
         <f>H30*F30</f>
         <v/>
       </c>
-      <c r="J30" s="62" t="n"/>
-      <c r="K30" s="63" t="n"/>
-    </row>
-    <row r="31" ht="20.1" customHeight="1" s="56">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="62" t="n"/>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="63" t="n"/>
-      <c r="E31" s="66" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" s="50">
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="55" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="28">
+      <c r="I31" s="62">
         <f>H31*F31</f>
         <v/>
       </c>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="63" t="n"/>
-    </row>
-    <row r="32" ht="20.1" customHeight="1" s="56">
-      <c r="A32" s="26" t="n"/>
-      <c r="B32" s="62" t="n"/>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="63" t="n"/>
-      <c r="E32" s="66" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" s="50">
+      <c r="A32" s="47" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="55" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="28">
+      <c r="I32" s="62">
         <f>H32*F32</f>
         <v/>
       </c>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="63" t="n"/>
-    </row>
-    <row r="33" ht="20.1" customHeight="1" s="56">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" s="50">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="B33" s="62" t="n"/>
-      <c r="C33" s="62" t="n"/>
-      <c r="D33" s="62" t="n"/>
-      <c r="E33" s="62" t="n"/>
-      <c r="F33" s="62" t="n"/>
-      <c r="G33" s="62" t="n"/>
-      <c r="H33" s="63" t="n"/>
-      <c r="I33" s="28">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="62">
         <f>SUM(I17:K32)</f>
         <v/>
       </c>
-      <c r="J33" s="62" t="n"/>
-      <c r="K33" s="63" t="n"/>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" s="56">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="26" t="n"/>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" s="50">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>消費税10％</t>
         </is>
       </c>
-      <c r="B34" s="62" t="n"/>
-      <c r="C34" s="62" t="n"/>
-      <c r="D34" s="62" t="n"/>
-      <c r="E34" s="62" t="n"/>
-      <c r="F34" s="62" t="n"/>
-      <c r="G34" s="62" t="n"/>
-      <c r="H34" s="63" t="n"/>
-      <c r="I34" s="19">
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="67">
         <f>I33*10%</f>
         <v/>
       </c>
-      <c r="J34" s="62" t="n"/>
-      <c r="K34" s="63" t="n"/>
-    </row>
-    <row r="35" ht="20.1" customHeight="1" s="56" thickBot="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="26" t="n"/>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="67" t="n"/>
-      <c r="C35" s="67" t="n"/>
-      <c r="D35" s="67" t="n"/>
-      <c r="E35" s="67" t="n"/>
-      <c r="F35" s="67" t="n"/>
-      <c r="G35" s="67" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="69">
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="29">
         <f>I33+I34</f>
         <v/>
       </c>
-      <c r="J35" s="67" t="n"/>
-      <c r="K35" s="74" t="n"/>
-    </row>
-    <row r="36" ht="20.1" customHeight="1" s="56">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" s="50">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>今後ともよろしくお願い申し上げます。</t>
         </is>
       </c>
-      <c r="B36" s="71" t="n"/>
-      <c r="C36" s="71" t="n"/>
-      <c r="D36" s="71" t="n"/>
-      <c r="E36" s="71" t="n"/>
-      <c r="F36" s="71" t="n"/>
-      <c r="G36" s="71" t="n"/>
-      <c r="H36" s="71" t="n"/>
-      <c r="I36" s="71" t="n"/>
-      <c r="J36" s="71" t="n"/>
-      <c r="K36" s="72" t="n"/>
-    </row>
-    <row r="37" ht="20.1" customHeight="1" s="56">
-      <c r="K37" s="73" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" s="56">
+    </row>
+    <row r="37" ht="20.1" customHeight="1" s="50"/>
+    <row r="38" ht="12" customHeight="1" s="50">
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -2925,10 +2866,10 @@
     <mergeCell ref="F1:G2"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="I34:K34"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="B3:D3"/>
@@ -2967,67 +2908,67 @@
   <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2" outlineLevelCol="0"/>
   <cols>
-    <col width="7.109375" customWidth="1" style="56" min="1" max="4"/>
-    <col width="12.44140625" customWidth="1" style="56" min="5" max="5"/>
-    <col width="6.6640625" customWidth="1" style="56" min="6" max="7"/>
-    <col width="9.6640625" customWidth="1" style="56" min="8" max="8"/>
-    <col width="8.109375" customWidth="1" style="56" min="9" max="9"/>
-    <col width="7.44140625" customWidth="1" style="56" min="10" max="10"/>
-    <col width="7.6640625" customWidth="1" style="56" min="11" max="14"/>
-    <col width="9.6640625" customWidth="1" style="56" min="15" max="15"/>
-    <col width="10.6640625" customWidth="1" style="56" min="16" max="16"/>
-    <col width="6.6640625" customWidth="1" style="56" min="17" max="17"/>
-    <col width="7.109375" customWidth="1" style="56" min="18" max="18"/>
-    <col width="8.6640625" customWidth="1" style="56" min="19" max="19"/>
-    <col width="7.6640625" customWidth="1" style="56" min="20" max="21"/>
-    <col width="7.44140625" customWidth="1" style="56" min="22" max="22"/>
-    <col width="9.21875" bestFit="1" customWidth="1" style="56" min="24" max="24"/>
+    <col width="7.109375" customWidth="1" style="50" min="1" max="4"/>
+    <col width="12.44140625" customWidth="1" style="50" min="5" max="5"/>
+    <col width="6.6640625" customWidth="1" style="50" min="6" max="7"/>
+    <col width="9.6640625" customWidth="1" style="50" min="8" max="8"/>
+    <col width="8.109375" customWidth="1" style="50" min="9" max="9"/>
+    <col width="7.44140625" customWidth="1" style="50" min="10" max="10"/>
+    <col width="7.6640625" customWidth="1" style="50" min="11" max="14"/>
+    <col width="9.6640625" customWidth="1" style="50" min="15" max="15"/>
+    <col width="10.6640625" customWidth="1" style="50" min="16" max="16"/>
+    <col width="6.6640625" customWidth="1" style="50" min="17" max="17"/>
+    <col width="7.109375" customWidth="1" style="50" min="18" max="18"/>
+    <col width="8.6640625" customWidth="1" style="50" min="19" max="19"/>
+    <col width="7.6640625" customWidth="1" style="50" min="20" max="21"/>
+    <col width="7.44140625" customWidth="1" style="50" min="22" max="22"/>
+    <col width="9.21875" bestFit="1" customWidth="1" style="50" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.9" customHeight="1" s="56">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="24.9" customHeight="1" s="50">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>サンエイ株式会社</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="48" t="inlineStr">
         <is>
           <t>営統事業部</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="I1" s="45" t="inlineStr">
+      <c r="I1" s="40" t="inlineStr">
         <is>
           <t>請求書</t>
         </is>
       </c>
-      <c r="L1" s="45" t="inlineStr">
+      <c r="L1" s="40" t="inlineStr">
         <is>
           <t>サンエイ株式会社</t>
         </is>
       </c>
-      <c r="O1" s="49" t="inlineStr">
+      <c r="O1" s="48" t="inlineStr">
         <is>
           <t>営統事業部</t>
         </is>
       </c>
-      <c r="Q1" s="44" t="inlineStr">
+      <c r="Q1" s="25" t="inlineStr">
         <is>
           <t>御中</t>
         </is>
       </c>
-      <c r="T1" s="45" t="inlineStr">
+      <c r="T1" s="40" t="inlineStr">
         <is>
           <t>請求明細書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24.9" customHeight="1" s="56">
-      <c r="D2" s="49" t="inlineStr">
+    <row r="2" ht="24.9" customHeight="1" s="50">
+      <c r="D2" s="48" t="inlineStr">
         <is>
           <t>建設課</t>
         </is>
@@ -3044,7 +2985,7 @@
       </c>
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
-      <c r="O2" s="49" t="inlineStr">
+      <c r="O2" s="48" t="inlineStr">
         <is>
           <t>建設課</t>
         </is>
@@ -3062,13 +3003,13 @@
       <c r="U2" s="1" t="n"/>
       <c r="V2" s="1" t="n"/>
     </row>
-    <row r="3" ht="20.1" customHeight="1" s="56">
+    <row r="3" ht="20.1" customHeight="1" s="50">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>工事名</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>清掃応援工事</t>
         </is>
@@ -3078,24 +3019,24 @@
           <t>工事名</t>
         </is>
       </c>
-      <c r="M3" s="42" t="inlineStr">
+      <c r="M3" s="43" t="inlineStr">
         <is>
           <t>清掃応援工事</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" s="56">
+    <row r="4" ht="20.1" customHeight="1" s="50">
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>日付：</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>月　日〆</t>
         </is>
@@ -3105,36 +3046,36 @@
           <t>日付：</t>
         </is>
       </c>
-      <c r="T4" s="43" t="inlineStr">
+      <c r="T4" s="28" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="U4" s="43" t="inlineStr">
+      <c r="U4" s="28" t="inlineStr">
         <is>
           <t>月　日〆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20.1" customHeight="1" s="56">
-      <c r="A5" s="51" t="inlineStr">
+    <row r="5" ht="20.1" customHeight="1" s="50">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="J5" s="43" t="n"/>
-      <c r="L5" s="51" t="inlineStr">
+      <c r="J5" s="28" t="n"/>
+      <c r="L5" s="46" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
-      <c r="U5" s="43" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" s="56">
+      <c r="U5" s="28" t="n"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" s="50">
       <c r="E6" s="0" t="inlineStr">
         <is>
           <t>　　　</t>
@@ -3146,101 +3087,101 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20.1" customHeight="1" s="56"/>
-    <row r="8" ht="24.9" customHeight="1" s="56"/>
-    <row r="9" ht="24.9" customHeight="1" s="56">
-      <c r="A9" s="55" t="inlineStr">
+    <row r="7" ht="20.1" customHeight="1" s="50"/>
+    <row r="8" ht="24.9" customHeight="1" s="50"/>
+    <row r="9" ht="24.9" customHeight="1" s="50">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>住所：　愛知県豊橋市東森岡1-7-13</t>
         </is>
       </c>
-      <c r="G9" s="55" t="n"/>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>金融機関名：</t>
         </is>
       </c>
-      <c r="J9" s="39" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>豊橋信用金庫</t>
         </is>
       </c>
-      <c r="L9" s="55" t="inlineStr">
+      <c r="L9" s="42" t="inlineStr">
         <is>
           <t>住所：　愛知県豊橋市東森岡1-7-13</t>
         </is>
       </c>
-      <c r="R9" s="55" t="n"/>
-      <c r="S9" s="40" t="n"/>
-      <c r="U9" s="39" t="n"/>
-    </row>
-    <row r="10" ht="24.9" customHeight="1" s="56">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="R9" s="42" t="n"/>
+      <c r="S9" s="20" t="n"/>
+      <c r="U9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="24.9" customHeight="1" s="50">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　TEL:　　0532-88-7770</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>支店名　：</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>牛川支店・普通</t>
         </is>
       </c>
-      <c r="L10" s="54" t="inlineStr">
+      <c r="L10" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　TEL:　　0532-88-7770</t>
         </is>
       </c>
-      <c r="S10" s="40" t="n"/>
-      <c r="U10" s="39" t="n"/>
-    </row>
-    <row r="11" ht="24.9" customHeight="1" s="56">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="S10" s="20" t="n"/>
+      <c r="U10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="24.9" customHeight="1" s="50">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　FAX:　　0532-88-4591</t>
         </is>
       </c>
-      <c r="H11" s="40" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>口座名義：</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>株式会社　柚喜</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　FAX:　　0532-88-4591</t>
         </is>
       </c>
-      <c r="S11" s="40" t="n"/>
-      <c r="U11" s="39" t="n"/>
-    </row>
-    <row r="12" ht="24.9" customHeight="1" s="56">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="S11" s="20" t="n"/>
+      <c r="U11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="24.9" customHeight="1" s="50">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>E-MAIL:　cs-yuzuki0109@cd5.so-net.ne.ip</t>
         </is>
       </c>
-      <c r="H12" s="39" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　　　　　　代表取締役　藤澤　淳</t>
         </is>
       </c>
-      <c r="L12" s="55" t="inlineStr">
+      <c r="L12" s="42" t="inlineStr">
         <is>
           <t>E-MAIL:　cs-yuzuki0109@cd5.so-net.ne.ip</t>
         </is>
       </c>
-      <c r="S12" s="39" t="n"/>
-    </row>
-    <row r="13" ht="24.9" customHeight="1" s="56">
+      <c r="S12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="24.9" customHeight="1" s="50">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
@@ -3248,12 +3189,12 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="40" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>口座番号：</t>
         </is>
       </c>
-      <c r="J13" s="57" t="n">
+      <c r="J13" s="51" t="n">
         <v>372785</v>
       </c>
       <c r="L13" s="5" t="n"/>
@@ -3263,10 +3204,10 @@
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="40" t="n"/>
-      <c r="U13" s="57" t="n"/>
-    </row>
-    <row r="14" ht="20.1" customHeight="1" s="56">
+      <c r="S13" s="20" t="n"/>
+      <c r="U13" s="51" t="n"/>
+    </row>
+    <row r="14" ht="20.1" customHeight="1" s="50">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
@@ -3282,729 +3223,718 @@
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" s="56" thickBot="1">
+    <row r="15" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="C15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="56">
-      <c r="A16" s="58" t="inlineStr">
+    <row r="16" ht="21.75" customHeight="1" s="50">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="60" t="n"/>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="44" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="44" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="H16" s="37" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="I16" s="37" t="inlineStr">
+      <c r="I16" s="57" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="J16" s="59" t="n"/>
-      <c r="K16" s="60" t="n"/>
-      <c r="L16" s="58" t="inlineStr">
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
         </is>
       </c>
-      <c r="M16" s="59" t="n"/>
-      <c r="N16" s="59" t="n"/>
-      <c r="O16" s="60" t="n"/>
-      <c r="P16" s="37" t="inlineStr">
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="44" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="Q16" s="37" t="inlineStr">
+      <c r="Q16" s="44" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="37" t="inlineStr">
+      <c r="R16" s="57" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="37" t="inlineStr">
+      <c r="S16" s="57" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="37" t="inlineStr">
+      <c r="T16" s="57" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="U16" s="59" t="n"/>
-      <c r="V16" s="60" t="n"/>
-    </row>
-    <row r="17" ht="20.1" customHeight="1" s="56">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="U16" s="34" t="n"/>
+      <c r="V16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="20.1" customHeight="1" s="50">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>清掃応援工事</t>
         </is>
       </c>
-      <c r="B17" s="62" t="n"/>
-      <c r="C17" s="62" t="n"/>
-      <c r="D17" s="63" t="n"/>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="28">
+      <c r="I17" s="58">
         <f>T35</f>
         <v/>
       </c>
-      <c r="J17" s="62" t="n"/>
-      <c r="K17" s="63" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="62" t="n"/>
-      <c r="N17" s="62" t="n"/>
-      <c r="O17" s="63" t="n"/>
-      <c r="P17" s="64" t="n"/>
-      <c r="Q17" s="27" t="n"/>
-      <c r="R17" s="27" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="28">
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="53" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="63" t="n"/>
+      <c r="S17" s="64" t="n"/>
+      <c r="T17" s="58">
         <f>S17*Q17</f>
         <v/>
       </c>
-      <c r="U17" s="62" t="n"/>
-      <c r="V17" s="63" t="n"/>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" s="56">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="62" t="n"/>
-      <c r="C18" s="62" t="n"/>
-      <c r="D18" s="63" t="n"/>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
+      <c r="U17" s="18" t="n"/>
+      <c r="V17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" s="50">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n"/>
-      <c r="I18" s="28">
+      <c r="I18" s="58">
         <f>H18*F18</f>
         <v/>
       </c>
-      <c r="J18" s="62" t="n"/>
-      <c r="K18" s="63" t="n"/>
-      <c r="L18" s="29" t="n"/>
-      <c r="M18" s="62" t="n"/>
-      <c r="N18" s="62" t="n"/>
-      <c r="O18" s="63" t="n"/>
-      <c r="P18" s="64" t="n"/>
-      <c r="Q18" s="27" t="n"/>
-      <c r="R18" s="27" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="28">
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="53" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="63" t="n"/>
+      <c r="S18" s="64" t="n"/>
+      <c r="T18" s="58">
         <f>S18*Q18</f>
         <v/>
       </c>
-      <c r="U18" s="62" t="n"/>
-      <c r="V18" s="63" t="n"/>
-    </row>
-    <row r="19" ht="20.1" customHeight="1" s="56">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="62" t="n"/>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="63" t="n"/>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
+      <c r="U18" s="18" t="n"/>
+      <c r="V18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="50">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="28">
+      <c r="I19" s="58">
         <f>H19*F19</f>
         <v/>
       </c>
-      <c r="J19" s="62" t="n"/>
-      <c r="K19" s="63" t="n"/>
-      <c r="L19" s="29" t="n"/>
-      <c r="M19" s="62" t="n"/>
-      <c r="N19" s="62" t="n"/>
-      <c r="O19" s="63" t="n"/>
-      <c r="P19" s="64" t="n"/>
-      <c r="Q19" s="27" t="n"/>
-      <c r="R19" s="27" t="n"/>
-      <c r="S19" s="9" t="n"/>
-      <c r="T19" s="28">
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="18" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="53" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="63" t="n"/>
+      <c r="S19" s="64" t="n"/>
+      <c r="T19" s="58">
         <f>S19*Q19</f>
         <v/>
       </c>
-      <c r="U19" s="62" t="n"/>
-      <c r="V19" s="63" t="n"/>
-    </row>
-    <row r="20" ht="20.1" customHeight="1" s="56">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="63" t="n"/>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
+      <c r="U19" s="18" t="n"/>
+      <c r="V19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" s="50">
+      <c r="A20" s="22" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n"/>
-      <c r="I20" s="28">
+      <c r="I20" s="58">
         <f>H20*F20</f>
         <v/>
       </c>
-      <c r="J20" s="62" t="n"/>
-      <c r="K20" s="63" t="n"/>
-      <c r="L20" s="29" t="n"/>
-      <c r="M20" s="62" t="n"/>
-      <c r="N20" s="62" t="n"/>
-      <c r="O20" s="63" t="n"/>
-      <c r="P20" s="64" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="27" t="n"/>
-      <c r="S20" s="9" t="n"/>
-      <c r="T20" s="28">
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="53" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="63" t="n"/>
+      <c r="S20" s="64" t="n"/>
+      <c r="T20" s="58">
         <f>S20*Q20</f>
         <v/>
       </c>
-      <c r="U20" s="62" t="n"/>
-      <c r="V20" s="63" t="n"/>
-    </row>
-    <row r="21" ht="20.1" customHeight="1" s="56">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="62" t="n"/>
-      <c r="C21" s="62" t="n"/>
-      <c r="D21" s="63" t="n"/>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
+      <c r="U20" s="18" t="n"/>
+      <c r="V20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="20.1" customHeight="1" s="50">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="28">
+      <c r="I21" s="58">
         <f>H21*F21</f>
         <v/>
       </c>
-      <c r="J21" s="62" t="n"/>
-      <c r="K21" s="63" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="62" t="n"/>
-      <c r="N21" s="62" t="n"/>
-      <c r="O21" s="63" t="n"/>
-      <c r="P21" s="64" t="n"/>
-      <c r="Q21" s="27" t="n"/>
-      <c r="R21" s="27" t="n"/>
-      <c r="S21" s="9" t="n"/>
-      <c r="T21" s="28">
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="53" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="R21" s="63" t="n"/>
+      <c r="S21" s="64" t="n"/>
+      <c r="T21" s="58">
         <f>S21*Q21</f>
         <v/>
       </c>
-      <c r="U21" s="62" t="n"/>
-      <c r="V21" s="63" t="n"/>
-    </row>
-    <row r="22" ht="20.1" customHeight="1" s="56">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="62" t="n"/>
-      <c r="C22" s="62" t="n"/>
-      <c r="D22" s="63" t="n"/>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="50">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
-      <c r="I22" s="28">
+      <c r="I22" s="58">
         <f>H22*F22</f>
         <v/>
       </c>
-      <c r="J22" s="62" t="n"/>
-      <c r="K22" s="63" t="n"/>
-      <c r="L22" s="29" t="n"/>
-      <c r="M22" s="62" t="n"/>
-      <c r="N22" s="62" t="n"/>
-      <c r="O22" s="63" t="n"/>
-      <c r="P22" s="64" t="n"/>
-      <c r="Q22" s="27" t="n"/>
-      <c r="R22" s="27" t="n"/>
-      <c r="S22" s="9" t="n"/>
-      <c r="T22" s="28">
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="53" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="63" t="n"/>
+      <c r="S22" s="64" t="n"/>
+      <c r="T22" s="58">
         <f>S22*Q22</f>
         <v/>
       </c>
-      <c r="U22" s="62" t="n"/>
-      <c r="V22" s="63" t="n"/>
-    </row>
-    <row r="23" ht="20.1" customHeight="1" s="56">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="62" t="n"/>
-      <c r="C23" s="62" t="n"/>
-      <c r="D23" s="63" t="n"/>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
+      <c r="U22" s="18" t="n"/>
+      <c r="V22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" s="50">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="28">
+      <c r="I23" s="58">
         <f>H23*F23</f>
         <v/>
       </c>
-      <c r="J23" s="62" t="n"/>
-      <c r="K23" s="63" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="62" t="n"/>
-      <c r="N23" s="62" t="n"/>
-      <c r="O23" s="63" t="n"/>
-      <c r="P23" s="64" t="n"/>
-      <c r="Q23" s="27" t="n"/>
-      <c r="R23" s="27" t="n"/>
-      <c r="S23" s="9" t="n"/>
-      <c r="T23" s="28">
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="53" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="63" t="n"/>
+      <c r="S23" s="64" t="n"/>
+      <c r="T23" s="58">
         <f>S23*Q23</f>
         <v/>
       </c>
-      <c r="U23" s="62" t="n"/>
-      <c r="V23" s="63" t="n"/>
-    </row>
-    <row r="24" ht="20.1" customHeight="1" s="56">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="62" t="n"/>
-      <c r="C24" s="62" t="n"/>
-      <c r="D24" s="63" t="n"/>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
+      <c r="U23" s="18" t="n"/>
+      <c r="V23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1" s="50">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="28">
+      <c r="I24" s="58">
         <f>H24*F24</f>
         <v/>
       </c>
-      <c r="J24" s="62" t="n"/>
-      <c r="K24" s="63" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="62" t="n"/>
-      <c r="N24" s="62" t="n"/>
-      <c r="O24" s="63" t="n"/>
-      <c r="P24" s="64" t="n"/>
-      <c r="Q24" s="27" t="n"/>
-      <c r="R24" s="27" t="n"/>
-      <c r="S24" s="9" t="n"/>
-      <c r="T24" s="28">
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="19" t="n"/>
+      <c r="P24" s="53" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="63" t="n"/>
+      <c r="S24" s="64" t="n"/>
+      <c r="T24" s="58">
         <f>S24*Q24</f>
         <v/>
       </c>
-      <c r="U24" s="62" t="n"/>
-      <c r="V24" s="63" t="n"/>
-    </row>
-    <row r="25" ht="20.1" customHeight="1" s="56">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="62" t="n"/>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="63" t="n"/>
-      <c r="E25" s="64" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
+      <c r="U24" s="18" t="n"/>
+      <c r="V24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="20.1" customHeight="1" s="50">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="28">
+      <c r="I25" s="58">
         <f>H25*F25</f>
         <v/>
       </c>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="63" t="n"/>
-      <c r="L25" s="29" t="n"/>
-      <c r="M25" s="62" t="n"/>
-      <c r="N25" s="62" t="n"/>
-      <c r="O25" s="63" t="n"/>
-      <c r="P25" s="64" t="n"/>
-      <c r="Q25" s="27" t="n"/>
-      <c r="R25" s="27" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="28">
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="53" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="63" t="n"/>
+      <c r="S25" s="64" t="n"/>
+      <c r="T25" s="58">
         <f>S25*Q25</f>
         <v/>
       </c>
-      <c r="U25" s="62" t="n"/>
-      <c r="V25" s="63" t="n"/>
-    </row>
-    <row r="26" ht="20.1" customHeight="1" s="56">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="62" t="n"/>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="63" t="n"/>
-      <c r="E26" s="64" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
+      <c r="U25" s="18" t="n"/>
+      <c r="V25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="50">
+      <c r="A26" s="22" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="28">
+      <c r="I26" s="58">
         <f>H26*F26</f>
         <v/>
       </c>
-      <c r="J26" s="62" t="n"/>
-      <c r="K26" s="63" t="n"/>
-      <c r="L26" s="29" t="n"/>
-      <c r="M26" s="62" t="n"/>
-      <c r="N26" s="62" t="n"/>
-      <c r="O26" s="63" t="n"/>
-      <c r="P26" s="64" t="n"/>
-      <c r="Q26" s="27" t="n"/>
-      <c r="R26" s="27" t="n"/>
-      <c r="S26" s="9" t="n"/>
-      <c r="T26" s="28">
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="53" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="63" t="n"/>
+      <c r="S26" s="64" t="n"/>
+      <c r="T26" s="58">
         <f>S26*Q26</f>
         <v/>
       </c>
-      <c r="U26" s="62" t="n"/>
-      <c r="V26" s="63" t="n"/>
-    </row>
-    <row r="27" ht="20.1" customHeight="1" s="56">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="62" t="n"/>
-      <c r="C27" s="62" t="n"/>
-      <c r="D27" s="63" t="n"/>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
+      <c r="U26" s="18" t="n"/>
+      <c r="V26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="50">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="28">
+      <c r="I27" s="58">
         <f>H27*F27</f>
         <v/>
       </c>
-      <c r="J27" s="62" t="n"/>
-      <c r="K27" s="63" t="n"/>
-      <c r="L27" s="29" t="n"/>
-      <c r="M27" s="62" t="n"/>
-      <c r="N27" s="62" t="n"/>
-      <c r="O27" s="63" t="n"/>
-      <c r="P27" s="64" t="n"/>
-      <c r="Q27" s="27" t="n"/>
-      <c r="R27" s="27" t="n"/>
-      <c r="S27" s="9" t="n"/>
-      <c r="T27" s="28">
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="53" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="63" t="n"/>
+      <c r="S27" s="64" t="n"/>
+      <c r="T27" s="58">
         <f>S27*Q27</f>
         <v/>
       </c>
-      <c r="U27" s="62" t="n"/>
-      <c r="V27" s="63" t="n"/>
-    </row>
-    <row r="28" ht="20.1" customHeight="1" s="56">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="62" t="n"/>
-      <c r="C28" s="62" t="n"/>
-      <c r="D28" s="63" t="n"/>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="U27" s="18" t="n"/>
+      <c r="V27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="20.1" customHeight="1" s="50">
+      <c r="A28" s="22" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="28">
+      <c r="I28" s="58">
         <f>H28*F28</f>
         <v/>
       </c>
-      <c r="J28" s="62" t="n"/>
-      <c r="K28" s="63" t="n"/>
-      <c r="L28" s="29" t="n"/>
-      <c r="M28" s="62" t="n"/>
-      <c r="N28" s="62" t="n"/>
-      <c r="O28" s="63" t="n"/>
-      <c r="P28" s="64" t="n"/>
-      <c r="Q28" s="27" t="n"/>
-      <c r="R28" s="27" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="28">
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="19" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="19" t="n"/>
+      <c r="P28" s="53" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="63" t="n"/>
+      <c r="S28" s="64" t="n"/>
+      <c r="T28" s="58">
         <f>S28*Q28</f>
         <v/>
       </c>
-      <c r="U28" s="62" t="n"/>
-      <c r="V28" s="63" t="n"/>
-    </row>
-    <row r="29" ht="20.1" customHeight="1" s="56">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="62" t="n"/>
-      <c r="C29" s="62" t="n"/>
-      <c r="D29" s="63" t="n"/>
-      <c r="E29" s="64" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
+      <c r="U28" s="18" t="n"/>
+      <c r="V28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="20.1" customHeight="1" s="50">
+      <c r="A29" s="22" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="28">
+      <c r="I29" s="58">
         <f>H29*F29</f>
         <v/>
       </c>
-      <c r="J29" s="62" t="n"/>
-      <c r="K29" s="63" t="n"/>
-      <c r="L29" s="29" t="n"/>
-      <c r="M29" s="62" t="n"/>
-      <c r="N29" s="62" t="n"/>
-      <c r="O29" s="63" t="n"/>
-      <c r="P29" s="64" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
-      <c r="S29" s="10" t="n"/>
-      <c r="T29" s="28">
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="53" t="n"/>
+      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="63" t="n"/>
+      <c r="S29" s="65" t="n"/>
+      <c r="T29" s="58">
         <f>S29*Q29</f>
         <v/>
       </c>
-      <c r="U29" s="62" t="n"/>
-      <c r="V29" s="63" t="n"/>
-    </row>
-    <row r="30" ht="20.1" customHeight="1" s="56">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="62" t="n"/>
-      <c r="C30" s="62" t="n"/>
-      <c r="D30" s="63" t="n"/>
-      <c r="E30" s="66" t="n"/>
+      <c r="U29" s="18" t="n"/>
+      <c r="V29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" s="50">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="55" t="n"/>
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="28">
+      <c r="I30" s="58">
         <f>H30*F30</f>
         <v/>
       </c>
-      <c r="J30" s="62" t="n"/>
-      <c r="K30" s="63" t="n"/>
-      <c r="L30" s="29" t="n"/>
-      <c r="M30" s="62" t="n"/>
-      <c r="N30" s="62" t="n"/>
-      <c r="O30" s="63" t="n"/>
-      <c r="P30" s="66" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="19" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="19" t="n"/>
+      <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="10" t="n"/>
-      <c r="T30" s="28">
+      <c r="R30" s="66" t="n"/>
+      <c r="S30" s="65" t="n"/>
+      <c r="T30" s="58">
         <f>S30*Q30</f>
         <v/>
       </c>
-      <c r="U30" s="62" t="n"/>
-      <c r="V30" s="63" t="n"/>
-    </row>
-    <row r="31" ht="20.1" customHeight="1" s="56">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="62" t="n"/>
-      <c r="C31" s="62" t="n"/>
-      <c r="D31" s="63" t="n"/>
-      <c r="E31" s="66" t="n"/>
+      <c r="U30" s="18" t="n"/>
+      <c r="V30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" s="50">
+      <c r="A31" s="22" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="55" t="n"/>
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="28">
+      <c r="I31" s="58">
         <f>H31*F31</f>
         <v/>
       </c>
-      <c r="J31" s="62" t="n"/>
-      <c r="K31" s="63" t="n"/>
-      <c r="L31" s="29" t="n"/>
-      <c r="M31" s="62" t="n"/>
-      <c r="N31" s="62" t="n"/>
-      <c r="O31" s="63" t="n"/>
-      <c r="P31" s="66" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="10" t="n"/>
-      <c r="T31" s="28">
+      <c r="R31" s="66" t="n"/>
+      <c r="S31" s="65" t="n"/>
+      <c r="T31" s="58">
         <f>S31*Q31</f>
         <v/>
       </c>
-      <c r="U31" s="62" t="n"/>
-      <c r="V31" s="63" t="n"/>
-    </row>
-    <row r="32" ht="20.1" customHeight="1" s="56">
-      <c r="A32" s="26" t="n"/>
-      <c r="B32" s="62" t="n"/>
-      <c r="C32" s="62" t="n"/>
-      <c r="D32" s="63" t="n"/>
-      <c r="E32" s="66" t="n"/>
+      <c r="U31" s="18" t="n"/>
+      <c r="V31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="20.1" customHeight="1" s="50">
+      <c r="A32" s="47" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="55" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="28">
+      <c r="I32" s="58">
         <f>H32*F32</f>
         <v/>
       </c>
-      <c r="J32" s="62" t="n"/>
-      <c r="K32" s="63" t="n"/>
-      <c r="L32" s="47" t="n"/>
-      <c r="M32" s="62" t="n"/>
-      <c r="N32" s="62" t="n"/>
-      <c r="O32" s="63" t="n"/>
-      <c r="P32" s="66" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="19" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="19" t="n"/>
+      <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="28">
+      <c r="R32" s="66" t="n"/>
+      <c r="S32" s="66" t="n"/>
+      <c r="T32" s="58">
         <f>S32*Q32</f>
         <v/>
       </c>
-      <c r="U32" s="62" t="n"/>
-      <c r="V32" s="63" t="n"/>
-    </row>
-    <row r="33" ht="20.1" customHeight="1" s="56">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="U32" s="18" t="n"/>
+      <c r="V32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="20.1" customHeight="1" s="50">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="B33" s="62" t="n"/>
-      <c r="C33" s="62" t="n"/>
-      <c r="D33" s="62" t="n"/>
-      <c r="E33" s="62" t="n"/>
-      <c r="F33" s="62" t="n"/>
-      <c r="G33" s="62" t="n"/>
-      <c r="H33" s="63" t="n"/>
-      <c r="I33" s="28">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="58">
         <f>I17</f>
         <v/>
       </c>
-      <c r="J33" s="62" t="n"/>
-      <c r="K33" s="63" t="n"/>
-      <c r="L33" s="29" t="n"/>
-      <c r="M33" s="62" t="n"/>
-      <c r="N33" s="62" t="n"/>
-      <c r="O33" s="63" t="n"/>
-      <c r="P33" s="66" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="19" t="n"/>
+      <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="11" t="n"/>
-      <c r="S33" s="10" t="n"/>
-      <c r="T33" s="28">
+      <c r="R33" s="66" t="n"/>
+      <c r="S33" s="65" t="n"/>
+      <c r="T33" s="58">
         <f>S33*Q33</f>
         <v/>
       </c>
-      <c r="U33" s="62" t="n"/>
-      <c r="V33" s="63" t="n"/>
-    </row>
-    <row r="34" ht="20.1" customHeight="1" s="56">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="U33" s="18" t="n"/>
+      <c r="V33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" s="50">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>消費税10％</t>
         </is>
       </c>
-      <c r="B34" s="62" t="n"/>
-      <c r="C34" s="62" t="n"/>
-      <c r="D34" s="62" t="n"/>
-      <c r="E34" s="62" t="n"/>
-      <c r="F34" s="62" t="n"/>
-      <c r="G34" s="62" t="n"/>
-      <c r="H34" s="63" t="n"/>
-      <c r="I34" s="19">
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="59">
         <f>I33*10%</f>
         <v/>
       </c>
-      <c r="J34" s="62" t="n"/>
-      <c r="K34" s="63" t="n"/>
-      <c r="L34" s="47" t="n"/>
-      <c r="M34" s="62" t="n"/>
-      <c r="N34" s="62" t="n"/>
-      <c r="O34" s="63" t="n"/>
-      <c r="P34" s="66" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="19" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="19" t="n"/>
+      <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="11" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="28">
+      <c r="R34" s="66" t="n"/>
+      <c r="S34" s="66" t="n"/>
+      <c r="T34" s="58">
         <f>S34*Q34</f>
         <v/>
       </c>
-      <c r="U34" s="62" t="n"/>
-      <c r="V34" s="63" t="n"/>
-    </row>
-    <row r="35" ht="20.1" customHeight="1" s="56" thickBot="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="U34" s="18" t="n"/>
+      <c r="V34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="67" t="n"/>
-      <c r="C35" s="67" t="n"/>
-      <c r="D35" s="67" t="n"/>
-      <c r="E35" s="67" t="n"/>
-      <c r="F35" s="67" t="n"/>
-      <c r="G35" s="67" t="n"/>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="69">
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="60">
         <f>I33+I34</f>
         <v/>
       </c>
-      <c r="J35" s="67" t="n"/>
-      <c r="K35" s="74" t="n"/>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="36" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="M35" s="62" t="n"/>
-      <c r="N35" s="62" t="n"/>
-      <c r="O35" s="62" t="n"/>
-      <c r="P35" s="62" t="n"/>
-      <c r="Q35" s="62" t="n"/>
-      <c r="R35" s="62" t="n"/>
-      <c r="S35" s="63" t="n"/>
-      <c r="T35" s="28">
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="18" t="n"/>
+      <c r="S35" s="19" t="n"/>
+      <c r="T35" s="58">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
-      <c r="U35" s="62" t="n"/>
-      <c r="V35" s="63" t="n"/>
-    </row>
-    <row r="36" ht="20.1" customHeight="1" s="56">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="U35" s="18" t="n"/>
+      <c r="V35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="20.1" customHeight="1" s="50">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>今後ともよろしくお願い申し上げます。</t>
         </is>
       </c>
-      <c r="B36" s="71" t="n"/>
-      <c r="C36" s="71" t="n"/>
-      <c r="D36" s="71" t="n"/>
-      <c r="E36" s="71" t="n"/>
-      <c r="F36" s="71" t="n"/>
-      <c r="G36" s="71" t="n"/>
-      <c r="H36" s="71" t="n"/>
-      <c r="I36" s="71" t="n"/>
-      <c r="J36" s="71" t="n"/>
-      <c r="K36" s="72" t="n"/>
-      <c r="L36" s="17" t="inlineStr">
+      <c r="L36" s="36" t="inlineStr">
         <is>
           <t>消費税10％</t>
         </is>
       </c>
-      <c r="M36" s="62" t="n"/>
-      <c r="N36" s="62" t="n"/>
-      <c r="O36" s="62" t="n"/>
-      <c r="P36" s="62" t="n"/>
-      <c r="Q36" s="62" t="n"/>
-      <c r="R36" s="62" t="n"/>
-      <c r="S36" s="63" t="n"/>
-      <c r="T36" s="19">
+      <c r="M36" s="18" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="R36" s="18" t="n"/>
+      <c r="S36" s="19" t="n"/>
+      <c r="T36" s="59">
         <f>T35*10%</f>
         <v/>
       </c>
-      <c r="U36" s="62" t="n"/>
-      <c r="V36" s="63" t="n"/>
-    </row>
-    <row r="37" ht="20.1" customHeight="1" s="56" thickBot="1">
-      <c r="K37" s="73" t="n"/>
-      <c r="L37" s="21" t="inlineStr">
+      <c r="U36" s="18" t="n"/>
+      <c r="V36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
+      <c r="L37" s="38" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="M37" s="67" t="n"/>
-      <c r="N37" s="67" t="n"/>
-      <c r="O37" s="67" t="n"/>
-      <c r="P37" s="67" t="n"/>
-      <c r="Q37" s="67" t="n"/>
-      <c r="R37" s="67" t="n"/>
-      <c r="S37" s="68" t="n"/>
-      <c r="T37" s="69">
+      <c r="M37" s="30" t="n"/>
+      <c r="N37" s="30" t="n"/>
+      <c r="O37" s="30" t="n"/>
+      <c r="P37" s="30" t="n"/>
+      <c r="Q37" s="30" t="n"/>
+      <c r="R37" s="30" t="n"/>
+      <c r="S37" s="39" t="n"/>
+      <c r="T37" s="60">
         <f>T35+T36</f>
         <v/>
       </c>
-      <c r="U37" s="67" t="n"/>
-      <c r="V37" s="74" t="n"/>
-    </row>
-    <row r="38" ht="12" customHeight="1" s="56">
+      <c r="U37" s="30" t="n"/>
+      <c r="V37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="12" customHeight="1" s="50">
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
@@ -4037,8 +3967,8 @@
     <mergeCell ref="L34:O34"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="L27:O27"/>
-    <mergeCell ref="J9:K9"/>
     <mergeCell ref="I24:K24"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A1:C2"/>
@@ -4134,8 +4064,8 @@
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="Q1:R2"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="L25:O25"/>
     <mergeCell ref="T25:V25"/>
-    <mergeCell ref="L25:O25"/>
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="A23:D23"/>

--- a/public/請求書テンプレ.xlsx
+++ b/public/請求書テンプレ.xlsx
@@ -157,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -530,6 +530,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -542,7 +568,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +742,21 @@
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1437,23 +1478,23 @@
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="57" t="inlineStr">
+      <c r="R16" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="57" t="inlineStr">
+      <c r="S16" s="68" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="57" t="inlineStr">
+      <c r="T16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="U16" s="34" t="n"/>
-      <c r="V16" s="35" t="n"/>
+      <c r="V16" s="45" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" s="50">
       <c r="A17" s="22" t="inlineStr">
@@ -1480,14 +1521,14 @@
       <c r="O17" s="19" t="n"/>
       <c r="P17" s="53" t="n"/>
       <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="63" t="n"/>
-      <c r="S17" s="64" t="n"/>
-      <c r="T17" s="58">
+      <c r="R17" s="69" t="n"/>
+      <c r="S17" s="70" t="n"/>
+      <c r="T17" s="62">
         <f>S17*Q17</f>
         <v/>
       </c>
       <c r="U17" s="18" t="n"/>
-      <c r="V17" s="19" t="n"/>
+      <c r="V17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="50">
       <c r="A18" s="22" t="n"/>
@@ -1510,14 +1551,14 @@
       <c r="O18" s="19" t="n"/>
       <c r="P18" s="53" t="n"/>
       <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="63" t="n"/>
-      <c r="S18" s="64" t="n"/>
-      <c r="T18" s="58">
+      <c r="R18" s="69" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="T18" s="62">
         <f>S18*Q18</f>
         <v/>
       </c>
       <c r="U18" s="18" t="n"/>
-      <c r="V18" s="19" t="n"/>
+      <c r="V18" s="26" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" s="50">
       <c r="A19" s="22" t="n"/>
@@ -1540,14 +1581,14 @@
       <c r="O19" s="19" t="n"/>
       <c r="P19" s="53" t="n"/>
       <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="63" t="n"/>
-      <c r="S19" s="64" t="n"/>
-      <c r="T19" s="58">
+      <c r="R19" s="69" t="n"/>
+      <c r="S19" s="70" t="n"/>
+      <c r="T19" s="62">
         <f>S19*Q19</f>
         <v/>
       </c>
       <c r="U19" s="18" t="n"/>
-      <c r="V19" s="19" t="n"/>
+      <c r="V19" s="26" t="n"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="50">
       <c r="A20" s="22" t="n"/>
@@ -1570,14 +1611,14 @@
       <c r="O20" s="19" t="n"/>
       <c r="P20" s="53" t="n"/>
       <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="63" t="n"/>
-      <c r="S20" s="64" t="n"/>
-      <c r="T20" s="58">
+      <c r="R20" s="69" t="n"/>
+      <c r="S20" s="70" t="n"/>
+      <c r="T20" s="62">
         <f>S20*Q20</f>
         <v/>
       </c>
       <c r="U20" s="18" t="n"/>
-      <c r="V20" s="19" t="n"/>
+      <c r="V20" s="26" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="50">
       <c r="A21" s="22" t="n"/>
@@ -1600,14 +1641,14 @@
       <c r="O21" s="19" t="n"/>
       <c r="P21" s="53" t="n"/>
       <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="63" t="n"/>
-      <c r="S21" s="64" t="n"/>
-      <c r="T21" s="58">
+      <c r="R21" s="69" t="n"/>
+      <c r="S21" s="70" t="n"/>
+      <c r="T21" s="62">
         <f>S21*Q21</f>
         <v/>
       </c>
       <c r="U21" s="18" t="n"/>
-      <c r="V21" s="19" t="n"/>
+      <c r="V21" s="26" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="50">
       <c r="A22" s="22" t="n"/>
@@ -1630,14 +1671,14 @@
       <c r="O22" s="19" t="n"/>
       <c r="P22" s="53" t="n"/>
       <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="63" t="n"/>
-      <c r="S22" s="64" t="n"/>
-      <c r="T22" s="58">
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="70" t="n"/>
+      <c r="T22" s="62">
         <f>S22*Q22</f>
         <v/>
       </c>
       <c r="U22" s="18" t="n"/>
-      <c r="V22" s="19" t="n"/>
+      <c r="V22" s="26" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="50">
       <c r="A23" s="22" t="n"/>
@@ -1660,14 +1701,14 @@
       <c r="O23" s="19" t="n"/>
       <c r="P23" s="53" t="n"/>
       <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="63" t="n"/>
-      <c r="S23" s="64" t="n"/>
-      <c r="T23" s="58">
+      <c r="R23" s="69" t="n"/>
+      <c r="S23" s="70" t="n"/>
+      <c r="T23" s="62">
         <f>S23*Q23</f>
         <v/>
       </c>
       <c r="U23" s="18" t="n"/>
-      <c r="V23" s="19" t="n"/>
+      <c r="V23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="50">
       <c r="A24" s="22" t="n"/>
@@ -1690,14 +1731,14 @@
       <c r="O24" s="19" t="n"/>
       <c r="P24" s="53" t="n"/>
       <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="63" t="n"/>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="58">
+      <c r="R24" s="69" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="T24" s="62">
         <f>S24*Q24</f>
         <v/>
       </c>
       <c r="U24" s="18" t="n"/>
-      <c r="V24" s="19" t="n"/>
+      <c r="V24" s="26" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" s="50">
       <c r="A25" s="22" t="n"/>
@@ -1720,14 +1761,14 @@
       <c r="O25" s="19" t="n"/>
       <c r="P25" s="53" t="n"/>
       <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="63" t="n"/>
-      <c r="S25" s="64" t="n"/>
-      <c r="T25" s="58">
+      <c r="R25" s="69" t="n"/>
+      <c r="S25" s="70" t="n"/>
+      <c r="T25" s="62">
         <f>S25*Q25</f>
         <v/>
       </c>
       <c r="U25" s="18" t="n"/>
-      <c r="V25" s="19" t="n"/>
+      <c r="V25" s="26" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" s="50">
       <c r="A26" s="22" t="n"/>
@@ -1750,14 +1791,14 @@
       <c r="O26" s="19" t="n"/>
       <c r="P26" s="53" t="n"/>
       <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="63" t="n"/>
-      <c r="S26" s="64" t="n"/>
-      <c r="T26" s="58">
+      <c r="R26" s="69" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="62">
         <f>S26*Q26</f>
         <v/>
       </c>
       <c r="U26" s="18" t="n"/>
-      <c r="V26" s="19" t="n"/>
+      <c r="V26" s="26" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="50">
       <c r="A27" s="22" t="n"/>
@@ -1780,14 +1821,14 @@
       <c r="O27" s="19" t="n"/>
       <c r="P27" s="53" t="n"/>
       <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="63" t="n"/>
-      <c r="S27" s="64" t="n"/>
-      <c r="T27" s="58">
+      <c r="R27" s="69" t="n"/>
+      <c r="S27" s="70" t="n"/>
+      <c r="T27" s="62">
         <f>S27*Q27</f>
         <v/>
       </c>
       <c r="U27" s="18" t="n"/>
-      <c r="V27" s="19" t="n"/>
+      <c r="V27" s="26" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="50">
       <c r="A28" s="22" t="n"/>
@@ -1810,14 +1851,14 @@
       <c r="O28" s="19" t="n"/>
       <c r="P28" s="53" t="n"/>
       <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="63" t="n"/>
-      <c r="S28" s="64" t="n"/>
-      <c r="T28" s="58">
+      <c r="R28" s="69" t="n"/>
+      <c r="S28" s="70" t="n"/>
+      <c r="T28" s="62">
         <f>S28*Q28</f>
         <v/>
       </c>
       <c r="U28" s="18" t="n"/>
-      <c r="V28" s="19" t="n"/>
+      <c r="V28" s="26" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="50">
       <c r="A29" s="22" t="n"/>
@@ -1840,14 +1881,14 @@
       <c r="O29" s="19" t="n"/>
       <c r="P29" s="53" t="n"/>
       <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="63" t="n"/>
-      <c r="S29" s="65" t="n"/>
-      <c r="T29" s="58">
+      <c r="R29" s="69" t="n"/>
+      <c r="S29" s="71" t="n"/>
+      <c r="T29" s="62">
         <f>S29*Q29</f>
         <v/>
       </c>
       <c r="U29" s="18" t="n"/>
-      <c r="V29" s="19" t="n"/>
+      <c r="V29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="50">
       <c r="A30" s="22" t="n"/>
@@ -1870,14 +1911,14 @@
       <c r="O30" s="19" t="n"/>
       <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="66" t="n"/>
-      <c r="S30" s="65" t="n"/>
-      <c r="T30" s="58">
+      <c r="R30" s="72" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="62">
         <f>S30*Q30</f>
         <v/>
       </c>
       <c r="U30" s="18" t="n"/>
-      <c r="V30" s="19" t="n"/>
+      <c r="V30" s="26" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="50">
       <c r="A31" s="22" t="n"/>
@@ -1900,14 +1941,14 @@
       <c r="O31" s="19" t="n"/>
       <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="66" t="n"/>
-      <c r="S31" s="65" t="n"/>
-      <c r="T31" s="58">
+      <c r="R31" s="72" t="n"/>
+      <c r="S31" s="71" t="n"/>
+      <c r="T31" s="62">
         <f>S31*Q31</f>
         <v/>
       </c>
       <c r="U31" s="18" t="n"/>
-      <c r="V31" s="19" t="n"/>
+      <c r="V31" s="26" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="50">
       <c r="A32" s="47" t="n"/>
@@ -1930,14 +1971,14 @@
       <c r="O32" s="19" t="n"/>
       <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="66" t="n"/>
-      <c r="S32" s="66" t="n"/>
-      <c r="T32" s="58">
+      <c r="R32" s="72" t="n"/>
+      <c r="S32" s="72" t="n"/>
+      <c r="T32" s="62">
         <f>S32*Q32</f>
         <v/>
       </c>
       <c r="U32" s="18" t="n"/>
-      <c r="V32" s="19" t="n"/>
+      <c r="V32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="50">
       <c r="A33" s="36" t="inlineStr">
@@ -1964,14 +2005,14 @@
       <c r="O33" s="19" t="n"/>
       <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="66" t="n"/>
-      <c r="S33" s="65" t="n"/>
-      <c r="T33" s="58">
+      <c r="R33" s="72" t="n"/>
+      <c r="S33" s="71" t="n"/>
+      <c r="T33" s="62">
         <f>S33*Q33</f>
         <v/>
       </c>
       <c r="U33" s="18" t="n"/>
-      <c r="V33" s="19" t="n"/>
+      <c r="V33" s="26" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="50">
       <c r="A34" s="36" t="inlineStr">
@@ -1998,14 +2039,14 @@
       <c r="O34" s="19" t="n"/>
       <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="66" t="n"/>
-      <c r="S34" s="66" t="n"/>
-      <c r="T34" s="58">
+      <c r="R34" s="72" t="n"/>
+      <c r="S34" s="72" t="n"/>
+      <c r="T34" s="62">
         <f>S34*Q34</f>
         <v/>
       </c>
       <c r="U34" s="18" t="n"/>
-      <c r="V34" s="19" t="n"/>
+      <c r="V34" s="26" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="A35" s="38" t="inlineStr">
@@ -2038,12 +2079,12 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="19" t="n"/>
-      <c r="T35" s="58">
+      <c r="T35" s="62">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
       <c r="U35" s="18" t="n"/>
-      <c r="V35" s="19" t="n"/>
+      <c r="V35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" s="50">
       <c r="A36" s="49" t="inlineStr">
@@ -2063,12 +2104,12 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="19" t="n"/>
-      <c r="T36" s="59">
+      <c r="T36" s="67">
         <f>T35*10%</f>
         <v/>
       </c>
       <c r="U36" s="18" t="n"/>
-      <c r="V36" s="19" t="n"/>
+      <c r="V36" s="26" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="L37" s="38" t="inlineStr">
@@ -2083,7 +2124,7 @@
       <c r="Q37" s="30" t="n"/>
       <c r="R37" s="30" t="n"/>
       <c r="S37" s="39" t="n"/>
-      <c r="T37" s="60">
+      <c r="T37" s="29">
         <f>T35+T36</f>
         <v/>
       </c>
@@ -3256,13 +3297,13 @@
           <t>単価</t>
         </is>
       </c>
-      <c r="I16" s="57" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="J16" s="34" t="n"/>
-      <c r="K16" s="35" t="n"/>
+      <c r="K16" s="45" t="n"/>
       <c r="L16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
@@ -3281,23 +3322,23 @@
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="57" t="inlineStr">
+      <c r="R16" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="57" t="inlineStr">
+      <c r="S16" s="68" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="57" t="inlineStr">
+      <c r="T16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="U16" s="34" t="n"/>
-      <c r="V16" s="35" t="n"/>
+      <c r="V16" s="45" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" s="50">
       <c r="A17" s="22" t="inlineStr">
@@ -3312,26 +3353,26 @@
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="58">
+      <c r="I17" s="62">
         <f>T35</f>
         <v/>
       </c>
       <c r="J17" s="18" t="n"/>
-      <c r="K17" s="19" t="n"/>
+      <c r="K17" s="26" t="n"/>
       <c r="L17" s="22" t="n"/>
       <c r="M17" s="18" t="n"/>
       <c r="N17" s="18" t="n"/>
       <c r="O17" s="19" t="n"/>
       <c r="P17" s="53" t="n"/>
       <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="63" t="n"/>
-      <c r="S17" s="64" t="n"/>
-      <c r="T17" s="58">
+      <c r="R17" s="69" t="n"/>
+      <c r="S17" s="70" t="n"/>
+      <c r="T17" s="62">
         <f>S17*Q17</f>
         <v/>
       </c>
       <c r="U17" s="18" t="n"/>
-      <c r="V17" s="19" t="n"/>
+      <c r="V17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="50">
       <c r="A18" s="22" t="n"/>
@@ -3342,26 +3383,26 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n"/>
-      <c r="I18" s="58">
+      <c r="I18" s="62">
         <f>H18*F18</f>
         <v/>
       </c>
       <c r="J18" s="18" t="n"/>
-      <c r="K18" s="19" t="n"/>
+      <c r="K18" s="26" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="18" t="n"/>
       <c r="N18" s="18" t="n"/>
       <c r="O18" s="19" t="n"/>
       <c r="P18" s="53" t="n"/>
       <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="63" t="n"/>
-      <c r="S18" s="64" t="n"/>
-      <c r="T18" s="58">
+      <c r="R18" s="69" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="T18" s="62">
         <f>S18*Q18</f>
         <v/>
       </c>
       <c r="U18" s="18" t="n"/>
-      <c r="V18" s="19" t="n"/>
+      <c r="V18" s="26" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" s="50">
       <c r="A19" s="22" t="n"/>
@@ -3372,26 +3413,26 @@
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="58">
+      <c r="I19" s="62">
         <f>H19*F19</f>
         <v/>
       </c>
       <c r="J19" s="18" t="n"/>
-      <c r="K19" s="19" t="n"/>
+      <c r="K19" s="26" t="n"/>
       <c r="L19" s="22" t="n"/>
       <c r="M19" s="18" t="n"/>
       <c r="N19" s="18" t="n"/>
       <c r="O19" s="19" t="n"/>
       <c r="P19" s="53" t="n"/>
       <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="63" t="n"/>
-      <c r="S19" s="64" t="n"/>
-      <c r="T19" s="58">
+      <c r="R19" s="69" t="n"/>
+      <c r="S19" s="70" t="n"/>
+      <c r="T19" s="62">
         <f>S19*Q19</f>
         <v/>
       </c>
       <c r="U19" s="18" t="n"/>
-      <c r="V19" s="19" t="n"/>
+      <c r="V19" s="26" t="n"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="50">
       <c r="A20" s="22" t="n"/>
@@ -3402,26 +3443,26 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n"/>
-      <c r="I20" s="58">
+      <c r="I20" s="62">
         <f>H20*F20</f>
         <v/>
       </c>
       <c r="J20" s="18" t="n"/>
-      <c r="K20" s="19" t="n"/>
+      <c r="K20" s="26" t="n"/>
       <c r="L20" s="22" t="n"/>
       <c r="M20" s="18" t="n"/>
       <c r="N20" s="18" t="n"/>
       <c r="O20" s="19" t="n"/>
       <c r="P20" s="53" t="n"/>
       <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="63" t="n"/>
-      <c r="S20" s="64" t="n"/>
-      <c r="T20" s="58">
+      <c r="R20" s="69" t="n"/>
+      <c r="S20" s="70" t="n"/>
+      <c r="T20" s="62">
         <f>S20*Q20</f>
         <v/>
       </c>
       <c r="U20" s="18" t="n"/>
-      <c r="V20" s="19" t="n"/>
+      <c r="V20" s="26" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="50">
       <c r="A21" s="22" t="n"/>
@@ -3432,26 +3473,26 @@
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="58">
+      <c r="I21" s="62">
         <f>H21*F21</f>
         <v/>
       </c>
       <c r="J21" s="18" t="n"/>
-      <c r="K21" s="19" t="n"/>
+      <c r="K21" s="26" t="n"/>
       <c r="L21" s="22" t="n"/>
       <c r="M21" s="18" t="n"/>
       <c r="N21" s="18" t="n"/>
       <c r="O21" s="19" t="n"/>
       <c r="P21" s="53" t="n"/>
       <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="63" t="n"/>
-      <c r="S21" s="64" t="n"/>
-      <c r="T21" s="58">
+      <c r="R21" s="69" t="n"/>
+      <c r="S21" s="70" t="n"/>
+      <c r="T21" s="62">
         <f>S21*Q21</f>
         <v/>
       </c>
       <c r="U21" s="18" t="n"/>
-      <c r="V21" s="19" t="n"/>
+      <c r="V21" s="26" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="50">
       <c r="A22" s="22" t="n"/>
@@ -3462,26 +3503,26 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
-      <c r="I22" s="58">
+      <c r="I22" s="62">
         <f>H22*F22</f>
         <v/>
       </c>
       <c r="J22" s="18" t="n"/>
-      <c r="K22" s="19" t="n"/>
+      <c r="K22" s="26" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="18" t="n"/>
       <c r="N22" s="18" t="n"/>
       <c r="O22" s="19" t="n"/>
       <c r="P22" s="53" t="n"/>
       <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="63" t="n"/>
-      <c r="S22" s="64" t="n"/>
-      <c r="T22" s="58">
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="70" t="n"/>
+      <c r="T22" s="62">
         <f>S22*Q22</f>
         <v/>
       </c>
       <c r="U22" s="18" t="n"/>
-      <c r="V22" s="19" t="n"/>
+      <c r="V22" s="26" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="50">
       <c r="A23" s="22" t="n"/>
@@ -3492,26 +3533,26 @@
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="58">
+      <c r="I23" s="62">
         <f>H23*F23</f>
         <v/>
       </c>
       <c r="J23" s="18" t="n"/>
-      <c r="K23" s="19" t="n"/>
+      <c r="K23" s="26" t="n"/>
       <c r="L23" s="22" t="n"/>
       <c r="M23" s="18" t="n"/>
       <c r="N23" s="18" t="n"/>
       <c r="O23" s="19" t="n"/>
       <c r="P23" s="53" t="n"/>
       <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="63" t="n"/>
-      <c r="S23" s="64" t="n"/>
-      <c r="T23" s="58">
+      <c r="R23" s="69" t="n"/>
+      <c r="S23" s="70" t="n"/>
+      <c r="T23" s="62">
         <f>S23*Q23</f>
         <v/>
       </c>
       <c r="U23" s="18" t="n"/>
-      <c r="V23" s="19" t="n"/>
+      <c r="V23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="50">
       <c r="A24" s="22" t="n"/>
@@ -3522,26 +3563,26 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="58">
+      <c r="I24" s="62">
         <f>H24*F24</f>
         <v/>
       </c>
       <c r="J24" s="18" t="n"/>
-      <c r="K24" s="19" t="n"/>
+      <c r="K24" s="26" t="n"/>
       <c r="L24" s="22" t="n"/>
       <c r="M24" s="18" t="n"/>
       <c r="N24" s="18" t="n"/>
       <c r="O24" s="19" t="n"/>
       <c r="P24" s="53" t="n"/>
       <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="63" t="n"/>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="58">
+      <c r="R24" s="69" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="T24" s="62">
         <f>S24*Q24</f>
         <v/>
       </c>
       <c r="U24" s="18" t="n"/>
-      <c r="V24" s="19" t="n"/>
+      <c r="V24" s="26" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" s="50">
       <c r="A25" s="22" t="n"/>
@@ -3552,26 +3593,26 @@
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="58">
+      <c r="I25" s="62">
         <f>H25*F25</f>
         <v/>
       </c>
       <c r="J25" s="18" t="n"/>
-      <c r="K25" s="19" t="n"/>
+      <c r="K25" s="26" t="n"/>
       <c r="L25" s="22" t="n"/>
       <c r="M25" s="18" t="n"/>
       <c r="N25" s="18" t="n"/>
       <c r="O25" s="19" t="n"/>
       <c r="P25" s="53" t="n"/>
       <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="63" t="n"/>
-      <c r="S25" s="64" t="n"/>
-      <c r="T25" s="58">
+      <c r="R25" s="69" t="n"/>
+      <c r="S25" s="70" t="n"/>
+      <c r="T25" s="62">
         <f>S25*Q25</f>
         <v/>
       </c>
       <c r="U25" s="18" t="n"/>
-      <c r="V25" s="19" t="n"/>
+      <c r="V25" s="26" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" s="50">
       <c r="A26" s="22" t="n"/>
@@ -3582,26 +3623,26 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="58">
+      <c r="I26" s="62">
         <f>H26*F26</f>
         <v/>
       </c>
       <c r="J26" s="18" t="n"/>
-      <c r="K26" s="19" t="n"/>
+      <c r="K26" s="26" t="n"/>
       <c r="L26" s="22" t="n"/>
       <c r="M26" s="18" t="n"/>
       <c r="N26" s="18" t="n"/>
       <c r="O26" s="19" t="n"/>
       <c r="P26" s="53" t="n"/>
       <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="63" t="n"/>
-      <c r="S26" s="64" t="n"/>
-      <c r="T26" s="58">
+      <c r="R26" s="69" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="62">
         <f>S26*Q26</f>
         <v/>
       </c>
       <c r="U26" s="18" t="n"/>
-      <c r="V26" s="19" t="n"/>
+      <c r="V26" s="26" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="50">
       <c r="A27" s="22" t="n"/>
@@ -3612,26 +3653,26 @@
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="58">
+      <c r="I27" s="62">
         <f>H27*F27</f>
         <v/>
       </c>
       <c r="J27" s="18" t="n"/>
-      <c r="K27" s="19" t="n"/>
+      <c r="K27" s="26" t="n"/>
       <c r="L27" s="22" t="n"/>
       <c r="M27" s="18" t="n"/>
       <c r="N27" s="18" t="n"/>
       <c r="O27" s="19" t="n"/>
       <c r="P27" s="53" t="n"/>
       <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="63" t="n"/>
-      <c r="S27" s="64" t="n"/>
-      <c r="T27" s="58">
+      <c r="R27" s="69" t="n"/>
+      <c r="S27" s="70" t="n"/>
+      <c r="T27" s="62">
         <f>S27*Q27</f>
         <v/>
       </c>
       <c r="U27" s="18" t="n"/>
-      <c r="V27" s="19" t="n"/>
+      <c r="V27" s="26" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="50">
       <c r="A28" s="22" t="n"/>
@@ -3642,26 +3683,26 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="58">
+      <c r="I28" s="62">
         <f>H28*F28</f>
         <v/>
       </c>
       <c r="J28" s="18" t="n"/>
-      <c r="K28" s="19" t="n"/>
+      <c r="K28" s="26" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="18" t="n"/>
       <c r="N28" s="18" t="n"/>
       <c r="O28" s="19" t="n"/>
       <c r="P28" s="53" t="n"/>
       <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="63" t="n"/>
-      <c r="S28" s="64" t="n"/>
-      <c r="T28" s="58">
+      <c r="R28" s="69" t="n"/>
+      <c r="S28" s="70" t="n"/>
+      <c r="T28" s="62">
         <f>S28*Q28</f>
         <v/>
       </c>
       <c r="U28" s="18" t="n"/>
-      <c r="V28" s="19" t="n"/>
+      <c r="V28" s="26" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="50">
       <c r="A29" s="22" t="n"/>
@@ -3672,26 +3713,26 @@
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="58">
+      <c r="I29" s="62">
         <f>H29*F29</f>
         <v/>
       </c>
       <c r="J29" s="18" t="n"/>
-      <c r="K29" s="19" t="n"/>
+      <c r="K29" s="26" t="n"/>
       <c r="L29" s="22" t="n"/>
       <c r="M29" s="18" t="n"/>
       <c r="N29" s="18" t="n"/>
       <c r="O29" s="19" t="n"/>
       <c r="P29" s="53" t="n"/>
       <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="63" t="n"/>
-      <c r="S29" s="65" t="n"/>
-      <c r="T29" s="58">
+      <c r="R29" s="69" t="n"/>
+      <c r="S29" s="71" t="n"/>
+      <c r="T29" s="62">
         <f>S29*Q29</f>
         <v/>
       </c>
       <c r="U29" s="18" t="n"/>
-      <c r="V29" s="19" t="n"/>
+      <c r="V29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="50">
       <c r="A30" s="22" t="n"/>
@@ -3702,26 +3743,26 @@
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="58">
+      <c r="I30" s="62">
         <f>H30*F30</f>
         <v/>
       </c>
       <c r="J30" s="18" t="n"/>
-      <c r="K30" s="19" t="n"/>
+      <c r="K30" s="26" t="n"/>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="18" t="n"/>
       <c r="N30" s="18" t="n"/>
       <c r="O30" s="19" t="n"/>
       <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="66" t="n"/>
-      <c r="S30" s="65" t="n"/>
-      <c r="T30" s="58">
+      <c r="R30" s="72" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="62">
         <f>S30*Q30</f>
         <v/>
       </c>
       <c r="U30" s="18" t="n"/>
-      <c r="V30" s="19" t="n"/>
+      <c r="V30" s="26" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="50">
       <c r="A31" s="22" t="n"/>
@@ -3732,26 +3773,26 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="58">
+      <c r="I31" s="62">
         <f>H31*F31</f>
         <v/>
       </c>
       <c r="J31" s="18" t="n"/>
-      <c r="K31" s="19" t="n"/>
+      <c r="K31" s="26" t="n"/>
       <c r="L31" s="22" t="n"/>
       <c r="M31" s="18" t="n"/>
       <c r="N31" s="18" t="n"/>
       <c r="O31" s="19" t="n"/>
       <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="66" t="n"/>
-      <c r="S31" s="65" t="n"/>
-      <c r="T31" s="58">
+      <c r="R31" s="72" t="n"/>
+      <c r="S31" s="71" t="n"/>
+      <c r="T31" s="62">
         <f>S31*Q31</f>
         <v/>
       </c>
       <c r="U31" s="18" t="n"/>
-      <c r="V31" s="19" t="n"/>
+      <c r="V31" s="26" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="50">
       <c r="A32" s="47" t="n"/>
@@ -3762,26 +3803,26 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="58">
+      <c r="I32" s="62">
         <f>H32*F32</f>
         <v/>
       </c>
       <c r="J32" s="18" t="n"/>
-      <c r="K32" s="19" t="n"/>
+      <c r="K32" s="26" t="n"/>
       <c r="L32" s="24" t="n"/>
       <c r="M32" s="18" t="n"/>
       <c r="N32" s="18" t="n"/>
       <c r="O32" s="19" t="n"/>
       <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="66" t="n"/>
-      <c r="S32" s="66" t="n"/>
-      <c r="T32" s="58">
+      <c r="R32" s="72" t="n"/>
+      <c r="S32" s="72" t="n"/>
+      <c r="T32" s="62">
         <f>S32*Q32</f>
         <v/>
       </c>
       <c r="U32" s="18" t="n"/>
-      <c r="V32" s="19" t="n"/>
+      <c r="V32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="50">
       <c r="A33" s="36" t="inlineStr">
@@ -3796,26 +3837,26 @@
       <c r="F33" s="18" t="n"/>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="58">
+      <c r="I33" s="62">
         <f>I17</f>
         <v/>
       </c>
       <c r="J33" s="18" t="n"/>
-      <c r="K33" s="19" t="n"/>
+      <c r="K33" s="26" t="n"/>
       <c r="L33" s="22" t="n"/>
       <c r="M33" s="18" t="n"/>
       <c r="N33" s="18" t="n"/>
       <c r="O33" s="19" t="n"/>
       <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="66" t="n"/>
-      <c r="S33" s="65" t="n"/>
-      <c r="T33" s="58">
+      <c r="R33" s="72" t="n"/>
+      <c r="S33" s="71" t="n"/>
+      <c r="T33" s="62">
         <f>S33*Q33</f>
         <v/>
       </c>
       <c r="U33" s="18" t="n"/>
-      <c r="V33" s="19" t="n"/>
+      <c r="V33" s="26" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="50">
       <c r="A34" s="36" t="inlineStr">
@@ -3830,26 +3871,26 @@
       <c r="F34" s="18" t="n"/>
       <c r="G34" s="18" t="n"/>
       <c r="H34" s="19" t="n"/>
-      <c r="I34" s="59">
+      <c r="I34" s="67">
         <f>I33*10%</f>
         <v/>
       </c>
       <c r="J34" s="18" t="n"/>
-      <c r="K34" s="19" t="n"/>
+      <c r="K34" s="26" t="n"/>
       <c r="L34" s="24" t="n"/>
       <c r="M34" s="18" t="n"/>
       <c r="N34" s="18" t="n"/>
       <c r="O34" s="19" t="n"/>
       <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="66" t="n"/>
-      <c r="S34" s="66" t="n"/>
-      <c r="T34" s="58">
+      <c r="R34" s="72" t="n"/>
+      <c r="S34" s="72" t="n"/>
+      <c r="T34" s="62">
         <f>S34*Q34</f>
         <v/>
       </c>
       <c r="U34" s="18" t="n"/>
-      <c r="V34" s="19" t="n"/>
+      <c r="V34" s="26" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="A35" s="38" t="inlineStr">
@@ -3864,7 +3905,7 @@
       <c r="F35" s="30" t="n"/>
       <c r="G35" s="30" t="n"/>
       <c r="H35" s="39" t="n"/>
-      <c r="I35" s="60">
+      <c r="I35" s="29">
         <f>I33+I34</f>
         <v/>
       </c>
@@ -3882,12 +3923,12 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="19" t="n"/>
-      <c r="T35" s="58">
+      <c r="T35" s="62">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
       <c r="U35" s="18" t="n"/>
-      <c r="V35" s="19" t="n"/>
+      <c r="V35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" s="50">
       <c r="A36" s="49" t="inlineStr">
@@ -3907,12 +3948,12 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="19" t="n"/>
-      <c r="T36" s="59">
+      <c r="T36" s="67">
         <f>T35*10%</f>
         <v/>
       </c>
       <c r="U36" s="18" t="n"/>
-      <c r="V36" s="19" t="n"/>
+      <c r="V36" s="26" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="L37" s="38" t="inlineStr">
@@ -3927,7 +3968,7 @@
       <c r="Q37" s="30" t="n"/>
       <c r="R37" s="30" t="n"/>
       <c r="S37" s="39" t="n"/>
-      <c r="T37" s="60">
+      <c r="T37" s="29">
         <f>T35+T36</f>
         <v/>
       </c>
